--- a/examples/data/id.xlsx
+++ b/examples/data/id.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Document\Desktop\go-enrich-tool\examples\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\bioinformatic-packages\go-enrich-tool\examples\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73AAB75F-6403-4214-9FE1-78012FFD2FAD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C27C4B9-12F8-4860-8005-0A427E3EF983}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2227" uniqueCount="2227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3001" uniqueCount="3001">
   <si>
     <t>GeneID</t>
   </si>
@@ -6701,6 +6701,2328 @@
   </si>
   <si>
     <t>zds</t>
+  </si>
+  <si>
+    <t>RPL3</t>
+  </si>
+  <si>
+    <t>RPL37</t>
+  </si>
+  <si>
+    <t>rpl38</t>
+  </si>
+  <si>
+    <t>RPL8</t>
+  </si>
+  <si>
+    <t>rps16</t>
+  </si>
+  <si>
+    <t>RPS17</t>
+  </si>
+  <si>
+    <t>RPS25</t>
+  </si>
+  <si>
+    <t>RSI-1</t>
+  </si>
+  <si>
+    <t>SAM3</t>
+  </si>
+  <si>
+    <t>SAMDC</t>
+  </si>
+  <si>
+    <t>SAP1</t>
+  </si>
+  <si>
+    <t>SAP11</t>
+  </si>
+  <si>
+    <t>SAP13</t>
+  </si>
+  <si>
+    <t>SAP2</t>
+  </si>
+  <si>
+    <t>SAP3</t>
+  </si>
+  <si>
+    <t>SAP5</t>
+  </si>
+  <si>
+    <t>SAP8</t>
+  </si>
+  <si>
+    <t>SAP9</t>
+  </si>
+  <si>
+    <t>SAR2</t>
+  </si>
+  <si>
+    <t>SBP3</t>
+  </si>
+  <si>
+    <t>SBT1</t>
+  </si>
+  <si>
+    <t>sbt3</t>
+  </si>
+  <si>
+    <t>sbt4a</t>
+  </si>
+  <si>
+    <t>sbt4b</t>
+  </si>
+  <si>
+    <t>sbt4c</t>
+  </si>
+  <si>
+    <t>sbt4d</t>
+  </si>
+  <si>
+    <t>sbt4e</t>
+  </si>
+  <si>
+    <t>SCOA</t>
+  </si>
+  <si>
+    <t>SD1</t>
+  </si>
+  <si>
+    <t>SDH</t>
+  </si>
+  <si>
+    <t>SERK3A</t>
+  </si>
+  <si>
+    <t>SERK3B</t>
+  </si>
+  <si>
+    <t>SFP4</t>
+  </si>
+  <si>
+    <t>SFP5</t>
+  </si>
+  <si>
+    <t>SFP6</t>
+  </si>
+  <si>
+    <t>sfr2</t>
+  </si>
+  <si>
+    <t>SFT</t>
+  </si>
+  <si>
+    <t>SGS3</t>
+  </si>
+  <si>
+    <t>SGT1</t>
+  </si>
+  <si>
+    <t>SGT1-1</t>
+  </si>
+  <si>
+    <t>SHINE3</t>
+  </si>
+  <si>
+    <t>Shy</t>
+  </si>
+  <si>
+    <t>sig1</t>
+  </si>
+  <si>
+    <t>SIP</t>
+  </si>
+  <si>
+    <t>Sip1</t>
+  </si>
+  <si>
+    <t>SIP2-1</t>
+  </si>
+  <si>
+    <t>SIZ1</t>
+  </si>
+  <si>
+    <t>SK</t>
+  </si>
+  <si>
+    <t>SKP1</t>
+  </si>
+  <si>
+    <t>Sl3-MMP</t>
+  </si>
+  <si>
+    <t>SlABF4</t>
+  </si>
+  <si>
+    <t>SlADH10A9</t>
+  </si>
+  <si>
+    <t>SlADH11A4a</t>
+  </si>
+  <si>
+    <t>SlADH12A1</t>
+  </si>
+  <si>
+    <t>SlADH2B7d</t>
+  </si>
+  <si>
+    <t>SlAGL6</t>
+  </si>
+  <si>
+    <t>SlAKR1</t>
+  </si>
+  <si>
+    <t>SlAKR4B</t>
+  </si>
+  <si>
+    <t>SlALDH11A3a</t>
+  </si>
+  <si>
+    <t>SlALDH6B2</t>
+  </si>
+  <si>
+    <t>SlALMT4</t>
+  </si>
+  <si>
+    <t>SlALMT5</t>
+  </si>
+  <si>
+    <t>Slalpha-kGDH</t>
+  </si>
+  <si>
+    <t>SlArf_Xyl1</t>
+  </si>
+  <si>
+    <t>SlArf_Xyl3</t>
+  </si>
+  <si>
+    <t>SlATG8a</t>
+  </si>
+  <si>
+    <t>SlAucsia-2</t>
+  </si>
+  <si>
+    <t>SLBRC1A</t>
+  </si>
+  <si>
+    <t>SlBRC1a-like</t>
+  </si>
+  <si>
+    <t>SLBRC1b</t>
+  </si>
+  <si>
+    <t>SlC3H61</t>
+  </si>
+  <si>
+    <t>SlCaM1</t>
+  </si>
+  <si>
+    <t>SlCaM2</t>
+  </si>
+  <si>
+    <t>SlCaM3</t>
+  </si>
+  <si>
+    <t>SlCaM5</t>
+  </si>
+  <si>
+    <t>SlCaM6</t>
+  </si>
+  <si>
+    <t>SlCBL1</t>
+  </si>
+  <si>
+    <t>SlCIPK2</t>
+  </si>
+  <si>
+    <t>SlCKX1</t>
+  </si>
+  <si>
+    <t>SlCKX2</t>
+  </si>
+  <si>
+    <t>SlCKX3</t>
+  </si>
+  <si>
+    <t>SlCKX4</t>
+  </si>
+  <si>
+    <t>SlCKX5</t>
+  </si>
+  <si>
+    <t>SlCKX7</t>
+  </si>
+  <si>
+    <t>SlCOR413IM1</t>
+  </si>
+  <si>
+    <t>SlCPTBP</t>
+  </si>
+  <si>
+    <t>SlCYC1</t>
+  </si>
+  <si>
+    <t>SlCYP735A1</t>
+  </si>
+  <si>
+    <t>SlCYP735A2</t>
+  </si>
+  <si>
+    <t>SlDEAD30</t>
+  </si>
+  <si>
+    <t>SlDMR6-1</t>
+  </si>
+  <si>
+    <t>SlDof22</t>
+  </si>
+  <si>
+    <t>SlEOT2</t>
+  </si>
+  <si>
+    <t>SlEOT2-2</t>
+  </si>
+  <si>
+    <t>SlERF52</t>
+  </si>
+  <si>
+    <t>SlERFD2</t>
+  </si>
+  <si>
+    <t>SLF1</t>
+  </si>
+  <si>
+    <t>SLF11</t>
+  </si>
+  <si>
+    <t>SLF12</t>
+  </si>
+  <si>
+    <t>SLF13</t>
+  </si>
+  <si>
+    <t>SLF5</t>
+  </si>
+  <si>
+    <t>SlFBA1</t>
+  </si>
+  <si>
+    <t>SlFBA3</t>
+  </si>
+  <si>
+    <t>SlFBA4</t>
+  </si>
+  <si>
+    <t>SlFBA6</t>
+  </si>
+  <si>
+    <t>SlFBA7</t>
+  </si>
+  <si>
+    <t>SlFBA8</t>
+  </si>
+  <si>
+    <t>SlFKBP12</t>
+  </si>
+  <si>
+    <t>SlGGP-LIKE</t>
+  </si>
+  <si>
+    <t>SlGID2</t>
+  </si>
+  <si>
+    <t>SlGLR1.2</t>
+  </si>
+  <si>
+    <t>SlGLR2.2</t>
+  </si>
+  <si>
+    <t>SlGLR3.5</t>
+  </si>
+  <si>
+    <t>SlGPAT6</t>
+  </si>
+  <si>
+    <t>SlGRAS24</t>
+  </si>
+  <si>
+    <t>SlGRX22</t>
+  </si>
+  <si>
+    <t>SlHAM</t>
+  </si>
+  <si>
+    <t>SlHDA3</t>
+  </si>
+  <si>
+    <t>SlIAA27</t>
+  </si>
+  <si>
+    <t>SlIAA8</t>
+  </si>
+  <si>
+    <t>SlIAA9</t>
+  </si>
+  <si>
+    <t>SlIPT1</t>
+  </si>
+  <si>
+    <t>SlIPT2</t>
+  </si>
+  <si>
+    <t>SlIPT3</t>
+  </si>
+  <si>
+    <t>SlIPT4</t>
+  </si>
+  <si>
+    <t>SlIPT5</t>
+  </si>
+  <si>
+    <t>SlJAF13</t>
+  </si>
+  <si>
+    <t>SlLAX1</t>
+  </si>
+  <si>
+    <t>SlMMP2</t>
+  </si>
+  <si>
+    <t>SlMYB117</t>
+  </si>
+  <si>
+    <t>SlMYB21</t>
+  </si>
+  <si>
+    <t>SlPer1</t>
+  </si>
+  <si>
+    <t>SlRAV2</t>
+  </si>
+  <si>
+    <t>SlRPT4</t>
+  </si>
+  <si>
+    <t>SlSINA4</t>
+  </si>
+  <si>
+    <t>SlSRN1</t>
+  </si>
+  <si>
+    <t>SlSSR1</t>
+  </si>
+  <si>
+    <t>SlSUN23</t>
+  </si>
+  <si>
+    <t>SLTAB2</t>
+  </si>
+  <si>
+    <t>SlTIP2-2</t>
+  </si>
+  <si>
+    <t>SlUev1C</t>
+  </si>
+  <si>
+    <t>SlUev1D</t>
+  </si>
+  <si>
+    <t>SlVP2</t>
+  </si>
+  <si>
+    <t>SlVPE1</t>
+  </si>
+  <si>
+    <t>SlVPE2</t>
+  </si>
+  <si>
+    <t>SlVPE3</t>
+  </si>
+  <si>
+    <t>SlVPE4</t>
+  </si>
+  <si>
+    <t>SlVPE5</t>
+  </si>
+  <si>
+    <t>SlVTE5</t>
+  </si>
+  <si>
+    <t>SlWRKY2</t>
+  </si>
+  <si>
+    <t>SlWRKY30</t>
+  </si>
+  <si>
+    <t>SlWRKY33A</t>
+  </si>
+  <si>
+    <t>SlWRKY37</t>
+  </si>
+  <si>
+    <t>SlWRKY72b</t>
+  </si>
+  <si>
+    <t>SlZFP2</t>
+  </si>
+  <si>
+    <t>SNF1</t>
+  </si>
+  <si>
+    <t>SNF4</t>
+  </si>
+  <si>
+    <t>SO</t>
+  </si>
+  <si>
+    <t>SODCC.1</t>
+  </si>
+  <si>
+    <t>sos1</t>
+  </si>
+  <si>
+    <t>SOS2</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>SP5G</t>
+  </si>
+  <si>
+    <t>SP6A</t>
+  </si>
+  <si>
+    <t>SP9D</t>
+  </si>
+  <si>
+    <t>spdsyn</t>
+  </si>
+  <si>
+    <t>SPGB</t>
+  </si>
+  <si>
+    <t>sph1</t>
+  </si>
+  <si>
+    <t>SPL</t>
+  </si>
+  <si>
+    <t>SPM1</t>
+  </si>
+  <si>
+    <t>sps</t>
+  </si>
+  <si>
+    <t>spy</t>
+  </si>
+  <si>
+    <t>SQD1</t>
+  </si>
+  <si>
+    <t>SRG1</t>
+  </si>
+  <si>
+    <t>SRG2</t>
+  </si>
+  <si>
+    <t>SRK2C</t>
+  </si>
+  <si>
+    <t>SRP14</t>
+  </si>
+  <si>
+    <t>SRP54</t>
+  </si>
+  <si>
+    <t>SSADH</t>
+  </si>
+  <si>
+    <t>SSK2</t>
+  </si>
+  <si>
+    <t>SSK3</t>
+  </si>
+  <si>
+    <t>SSR1</t>
+  </si>
+  <si>
+    <t>SSR2</t>
+  </si>
+  <si>
+    <t>SSTLE1</t>
+  </si>
+  <si>
+    <t>ST1</t>
+  </si>
+  <si>
+    <t>ST2</t>
+  </si>
+  <si>
+    <t>st3</t>
+  </si>
+  <si>
+    <t>ST4.1</t>
+  </si>
+  <si>
+    <t>std1</t>
+  </si>
+  <si>
+    <t>Stig1</t>
+  </si>
+  <si>
+    <t>STP11</t>
+  </si>
+  <si>
+    <t>STP12</t>
+  </si>
+  <si>
+    <t>STP18</t>
+  </si>
+  <si>
+    <t>stv3</t>
+  </si>
+  <si>
+    <t>Style2.1</t>
+  </si>
+  <si>
+    <t>sumo</t>
+  </si>
+  <si>
+    <t>SUN</t>
+  </si>
+  <si>
+    <t>sus3</t>
+  </si>
+  <si>
+    <t>SUS4</t>
+  </si>
+  <si>
+    <t>SUT2</t>
+  </si>
+  <si>
+    <t>SUT4</t>
+  </si>
+  <si>
+    <t>Suv</t>
+  </si>
+  <si>
+    <t>SYMRK</t>
+  </si>
+  <si>
+    <t>T12</t>
+  </si>
+  <si>
+    <t>t19-8</t>
+  </si>
+  <si>
+    <t>t19-8-2</t>
+  </si>
+  <si>
+    <t>T6</t>
+  </si>
+  <si>
+    <t>TAG1</t>
+  </si>
+  <si>
+    <t>TAGL1</t>
+  </si>
+  <si>
+    <t>TAL</t>
+  </si>
+  <si>
+    <t>TAO2</t>
+  </si>
+  <si>
+    <t>TAP2</t>
+  </si>
+  <si>
+    <t>TAPG1</t>
+  </si>
+  <si>
+    <t>TAPG2</t>
+  </si>
+  <si>
+    <t>TAPG4</t>
+  </si>
+  <si>
+    <t>TAPG5</t>
+  </si>
+  <si>
+    <t>TBG1</t>
+  </si>
+  <si>
+    <t>TBG2</t>
+  </si>
+  <si>
+    <t>TBG3</t>
+  </si>
+  <si>
+    <t>TBG5</t>
+  </si>
+  <si>
+    <t>TBG6</t>
+  </si>
+  <si>
+    <t>tbn1</t>
+  </si>
+  <si>
+    <t>TBP1</t>
+  </si>
+  <si>
+    <t>TCP1</t>
+  </si>
+  <si>
+    <t>TCP10</t>
+  </si>
+  <si>
+    <t>TCP11</t>
+  </si>
+  <si>
+    <t>TCP12</t>
+  </si>
+  <si>
+    <t>TCP13</t>
+  </si>
+  <si>
+    <t>TCP14</t>
+  </si>
+  <si>
+    <t>TCP15</t>
+  </si>
+  <si>
+    <t>TCP16</t>
+  </si>
+  <si>
+    <t>TCP17</t>
+  </si>
+  <si>
+    <t>TCP19</t>
+  </si>
+  <si>
+    <t>TCP20</t>
+  </si>
+  <si>
+    <t>TCP21</t>
+  </si>
+  <si>
+    <t>TCP22</t>
+  </si>
+  <si>
+    <t>TCP23</t>
+  </si>
+  <si>
+    <t>TCP24</t>
+  </si>
+  <si>
+    <t>TCP3</t>
+  </si>
+  <si>
+    <t>TCP4</t>
+  </si>
+  <si>
+    <t>TCP5</t>
+  </si>
+  <si>
+    <t>TCP6</t>
+  </si>
+  <si>
+    <t>TCTP</t>
+  </si>
+  <si>
+    <t>TCTR1</t>
+  </si>
+  <si>
+    <t>TCTR2</t>
+  </si>
+  <si>
+    <t>TDR6</t>
+  </si>
+  <si>
+    <t>TDR8</t>
+  </si>
+  <si>
+    <t>TFIIIA</t>
+  </si>
+  <si>
+    <t>TFT1</t>
+  </si>
+  <si>
+    <t>tft10</t>
+  </si>
+  <si>
+    <t>TFT3</t>
+  </si>
+  <si>
+    <t>tft4</t>
+  </si>
+  <si>
+    <t>TFT6</t>
+  </si>
+  <si>
+    <t>tft8</t>
+  </si>
+  <si>
+    <t>tft9</t>
+  </si>
+  <si>
+    <t>TGAS118</t>
+  </si>
+  <si>
+    <t>TH1</t>
+  </si>
+  <si>
+    <t>TH2</t>
+  </si>
+  <si>
+    <t>TH3</t>
+  </si>
+  <si>
+    <t>THIC</t>
+  </si>
+  <si>
+    <t>THM1</t>
+  </si>
+  <si>
+    <t>THM16</t>
+  </si>
+  <si>
+    <t>THM27</t>
+  </si>
+  <si>
+    <t>THM6</t>
+  </si>
+  <si>
+    <t>THox2</t>
+  </si>
+  <si>
+    <t>THT1-3</t>
+  </si>
+  <si>
+    <t>THT1-4</t>
+  </si>
+  <si>
+    <t>THT7-1</t>
+  </si>
+  <si>
+    <t>THT7-8</t>
+  </si>
+  <si>
+    <t>TIM10</t>
+  </si>
+  <si>
+    <t>TIP</t>
+  </si>
+  <si>
+    <t>TKn3</t>
+  </si>
+  <si>
+    <t>TKR</t>
+  </si>
+  <si>
+    <t>TLRP</t>
+  </si>
+  <si>
+    <t>tm-2</t>
+  </si>
+  <si>
+    <t>TM29</t>
+  </si>
+  <si>
+    <t>TMP</t>
+  </si>
+  <si>
+    <t>TMP1</t>
+  </si>
+  <si>
+    <t>TMT</t>
+  </si>
+  <si>
+    <t>TMT2</t>
+  </si>
+  <si>
+    <t>TOC75-III</t>
+  </si>
+  <si>
+    <t>Tom52</t>
+  </si>
+  <si>
+    <t>TomloxE</t>
+  </si>
+  <si>
+    <t>TPG6</t>
+  </si>
+  <si>
+    <t>TPK1b</t>
+  </si>
+  <si>
+    <t>TPLD</t>
+  </si>
+  <si>
+    <t>TPP3</t>
+  </si>
+  <si>
+    <t>TPS1</t>
+  </si>
+  <si>
+    <t>TPS14</t>
+  </si>
+  <si>
+    <t>TPS16</t>
+  </si>
+  <si>
+    <t>TPS17</t>
+  </si>
+  <si>
+    <t>TPS24</t>
+  </si>
+  <si>
+    <t>TPS28</t>
+  </si>
+  <si>
+    <t>TPS3</t>
+  </si>
+  <si>
+    <t>TPS31</t>
+  </si>
+  <si>
+    <t>TPS32</t>
+  </si>
+  <si>
+    <t>TPS33</t>
+  </si>
+  <si>
+    <t>TPS35</t>
+  </si>
+  <si>
+    <t>TPS36</t>
+  </si>
+  <si>
+    <t>TPS37</t>
+  </si>
+  <si>
+    <t>TPS38</t>
+  </si>
+  <si>
+    <t>TPS39</t>
+  </si>
+  <si>
+    <t>TPS7</t>
+  </si>
+  <si>
+    <t>TPx1</t>
+  </si>
+  <si>
+    <t>TPX2</t>
+  </si>
+  <si>
+    <t>TRN1</t>
+  </si>
+  <si>
+    <t>TSI-1</t>
+  </si>
+  <si>
+    <t>TTS2</t>
+  </si>
+  <si>
+    <t>TUB</t>
+  </si>
+  <si>
+    <t>tVPS41</t>
+  </si>
+  <si>
+    <t>twi1</t>
+  </si>
+  <si>
+    <t>tXET-B1</t>
+  </si>
+  <si>
+    <t>tXET-B2</t>
+  </si>
+  <si>
+    <t>UBC</t>
+  </si>
+  <si>
+    <t>Ubc13-2</t>
+  </si>
+  <si>
+    <t>UBC3</t>
+  </si>
+  <si>
+    <t>ubi3</t>
+  </si>
+  <si>
+    <t>UCP</t>
+  </si>
+  <si>
+    <t>ureD</t>
+  </si>
+  <si>
+    <t>USP</t>
+  </si>
+  <si>
+    <t>VAHOX1</t>
+  </si>
+  <si>
+    <t>Ve1</t>
+  </si>
+  <si>
+    <t>Ve2</t>
+  </si>
+  <si>
+    <t>VGT1</t>
+  </si>
+  <si>
+    <t>VGT2</t>
+  </si>
+  <si>
+    <t>vicilin</t>
+  </si>
+  <si>
+    <t>VIF</t>
+  </si>
+  <si>
+    <t>VIN3</t>
+  </si>
+  <si>
+    <t>vis1</t>
+  </si>
+  <si>
+    <t>VKOR</t>
+  </si>
+  <si>
+    <t>vp1.1</t>
+  </si>
+  <si>
+    <t>vsf-1</t>
+  </si>
+  <si>
+    <t>wee1</t>
+  </si>
+  <si>
+    <t>Wfi1</t>
+  </si>
+  <si>
+    <t>Why3</t>
+  </si>
+  <si>
+    <t>Wiv-1</t>
+  </si>
+  <si>
+    <t>WRKY3</t>
+  </si>
+  <si>
+    <t>WRKY72</t>
+  </si>
+  <si>
+    <t>WRKY75</t>
+  </si>
+  <si>
+    <t>WRKY81</t>
+  </si>
+  <si>
+    <t>WRKYIId</t>
+  </si>
+  <si>
+    <t>WRKYIId-1</t>
+  </si>
+  <si>
+    <t>WRKYIId-4</t>
+  </si>
+  <si>
+    <t>wus</t>
+  </si>
+  <si>
+    <t>XIP1-1-beta</t>
+  </si>
+  <si>
+    <t>Xpo1</t>
+  </si>
+  <si>
+    <t>XRN4</t>
+  </si>
+  <si>
+    <t>XSP10</t>
+  </si>
+  <si>
+    <t>XTH3</t>
+  </si>
+  <si>
+    <t>XTH5</t>
+  </si>
+  <si>
+    <t>XTH6</t>
+  </si>
+  <si>
+    <t>XTH7</t>
+  </si>
+  <si>
+    <t>XTH9</t>
+  </si>
+  <si>
+    <t>yfe37</t>
+  </si>
+  <si>
+    <t>ypt2</t>
+  </si>
+  <si>
+    <t>ZEP</t>
+  </si>
+  <si>
+    <t>ZF2</t>
+  </si>
+  <si>
+    <t>ZIP</t>
+  </si>
+  <si>
+    <t>LyesC2p069</t>
+  </si>
+  <si>
+    <t>LyesC2p070</t>
+  </si>
+  <si>
+    <t>LyesC2p071</t>
+  </si>
+  <si>
+    <t>LyesC2p072</t>
+  </si>
+  <si>
+    <t>LyesC2p073</t>
+  </si>
+  <si>
+    <t>LyesC2p074</t>
+  </si>
+  <si>
+    <t>LyesC2p075</t>
+  </si>
+  <si>
+    <t>LyesC2p076</t>
+  </si>
+  <si>
+    <t>LyesC2p077</t>
+  </si>
+  <si>
+    <t>LyesC2p078</t>
+  </si>
+  <si>
+    <t>LyesC2p079</t>
+  </si>
+  <si>
+    <t>LyesC2p080</t>
+  </si>
+  <si>
+    <t>LyesC2p081</t>
+  </si>
+  <si>
+    <t>LyesC2p082</t>
+  </si>
+  <si>
+    <t>LyesC2p083</t>
+  </si>
+  <si>
+    <t>LyesC2p084</t>
+  </si>
+  <si>
+    <t>LyesC2p085</t>
+  </si>
+  <si>
+    <t>LyesC2p086</t>
+  </si>
+  <si>
+    <t>LyesC2p087</t>
+  </si>
+  <si>
+    <t>LyesC2p088</t>
+  </si>
+  <si>
+    <t>LyesC2p089</t>
+  </si>
+  <si>
+    <t>LYR</t>
+  </si>
+  <si>
+    <t>MADS-RIN</t>
+  </si>
+  <si>
+    <t>MADS-RIN-MADS-MC</t>
+  </si>
+  <si>
+    <t>MAF1</t>
+  </si>
+  <si>
+    <t>MAN1</t>
+  </si>
+  <si>
+    <t>Man4</t>
+  </si>
+  <si>
+    <t>MAPK10</t>
+  </si>
+  <si>
+    <t>MAPK12</t>
+  </si>
+  <si>
+    <t>MAPK14</t>
+  </si>
+  <si>
+    <t>MAPK16</t>
+  </si>
+  <si>
+    <t>MAPK4</t>
+  </si>
+  <si>
+    <t>MAPK5</t>
+  </si>
+  <si>
+    <t>MAPK6</t>
+  </si>
+  <si>
+    <t>MAPK7</t>
+  </si>
+  <si>
+    <t>MAPKKKalpha</t>
+  </si>
+  <si>
+    <t>MAPKKKe</t>
+  </si>
+  <si>
+    <t>matriochka</t>
+  </si>
+  <si>
+    <t>MBD5</t>
+  </si>
+  <si>
+    <t>MBF1</t>
+  </si>
+  <si>
+    <t>MBF1a</t>
+  </si>
+  <si>
+    <t>MBF1c</t>
+  </si>
+  <si>
+    <t>MCA1</t>
+  </si>
+  <si>
+    <t>mcpi</t>
+  </si>
+  <si>
+    <t>MDC</t>
+  </si>
+  <si>
+    <t>MDHAR</t>
+  </si>
+  <si>
+    <t>Mdip1</t>
+  </si>
+  <si>
+    <t>ME2</t>
+  </si>
+  <si>
+    <t>mek1</t>
+  </si>
+  <si>
+    <t>MET</t>
+  </si>
+  <si>
+    <t>MFP1</t>
+  </si>
+  <si>
+    <t>MHX</t>
+  </si>
+  <si>
+    <t>Mi-1B</t>
+  </si>
+  <si>
+    <t>Mi-1C</t>
+  </si>
+  <si>
+    <t>Mi-1E</t>
+  </si>
+  <si>
+    <t>Mi-1F</t>
+  </si>
+  <si>
+    <t>Mi-1G</t>
+  </si>
+  <si>
+    <t>MKK2</t>
+  </si>
+  <si>
+    <t>MKK3</t>
+  </si>
+  <si>
+    <t>MKK4</t>
+  </si>
+  <si>
+    <t>MKS1a</t>
+  </si>
+  <si>
+    <t>MKS1b</t>
+  </si>
+  <si>
+    <t>MKS1d</t>
+  </si>
+  <si>
+    <t>MKS1e</t>
+  </si>
+  <si>
+    <t>MKS2</t>
+  </si>
+  <si>
+    <t>MKS2b</t>
+  </si>
+  <si>
+    <t>MKS2c</t>
+  </si>
+  <si>
+    <t>MLH1</t>
+  </si>
+  <si>
+    <t>MLO1</t>
+  </si>
+  <si>
+    <t>MLO2</t>
+  </si>
+  <si>
+    <t>mMDH1</t>
+  </si>
+  <si>
+    <t>mMDH2</t>
+  </si>
+  <si>
+    <t>MPK2</t>
+  </si>
+  <si>
+    <t>MPK3</t>
+  </si>
+  <si>
+    <t>MPK9</t>
+  </si>
+  <si>
+    <t>mpka1_3B1</t>
+  </si>
+  <si>
+    <t>MSH1</t>
+  </si>
+  <si>
+    <t>MSH2</t>
+  </si>
+  <si>
+    <t>MSI1</t>
+  </si>
+  <si>
+    <t>MSRA3</t>
+  </si>
+  <si>
+    <t>MSRA4</t>
+  </si>
+  <si>
+    <t>MSRA5</t>
+  </si>
+  <si>
+    <t>MST1</t>
+  </si>
+  <si>
+    <t>MST2</t>
+  </si>
+  <si>
+    <t>MT3</t>
+  </si>
+  <si>
+    <t>MT4</t>
+  </si>
+  <si>
+    <t>MTA</t>
+  </si>
+  <si>
+    <t>MTS1</t>
+  </si>
+  <si>
+    <t>MTS2</t>
+  </si>
+  <si>
+    <t>MTSHP</t>
+  </si>
+  <si>
+    <t>MYB</t>
+  </si>
+  <si>
+    <t>MYC1</t>
+  </si>
+  <si>
+    <t>MYC2</t>
+  </si>
+  <si>
+    <t>NAC-NOR</t>
+  </si>
+  <si>
+    <t>NAC1</t>
+  </si>
+  <si>
+    <t>NAC3</t>
+  </si>
+  <si>
+    <t>NACMTF2</t>
+  </si>
+  <si>
+    <t>NACMTF3</t>
+  </si>
+  <si>
+    <t>NAGK</t>
+  </si>
+  <si>
+    <t>NAM</t>
+  </si>
+  <si>
+    <t>NAM1</t>
+  </si>
+  <si>
+    <t>NAOAT</t>
+  </si>
+  <si>
+    <t>NDK</t>
+  </si>
+  <si>
+    <t>NDPS1</t>
+  </si>
+  <si>
+    <t>NHX1</t>
+  </si>
+  <si>
+    <t>NHX2</t>
+  </si>
+  <si>
+    <t>nhx3</t>
+  </si>
+  <si>
+    <t>nhx4</t>
+  </si>
+  <si>
+    <t>NIM1</t>
+  </si>
+  <si>
+    <t>NITF</t>
+  </si>
+  <si>
+    <t>NML1</t>
+  </si>
+  <si>
+    <t>NML2</t>
+  </si>
+  <si>
+    <t>NMP1</t>
+  </si>
+  <si>
+    <t>novel.1</t>
+  </si>
+  <si>
+    <t>novel.1002</t>
+  </si>
+  <si>
+    <t>novel.1003</t>
+  </si>
+  <si>
+    <t>novel.101</t>
+  </si>
+  <si>
+    <t>novel.1013</t>
+  </si>
+  <si>
+    <t>novel.1014</t>
+  </si>
+  <si>
+    <t>novel.1015</t>
+  </si>
+  <si>
+    <t>novel.1016</t>
+  </si>
+  <si>
+    <t>novel.1018</t>
+  </si>
+  <si>
+    <t>novel.1020</t>
+  </si>
+  <si>
+    <t>novel.1021</t>
+  </si>
+  <si>
+    <t>novel.1023</t>
+  </si>
+  <si>
+    <t>novel.1027</t>
+  </si>
+  <si>
+    <t>novel.1028</t>
+  </si>
+  <si>
+    <t>novel.1033</t>
+  </si>
+  <si>
+    <t>novel.1036</t>
+  </si>
+  <si>
+    <t>novel.1045</t>
+  </si>
+  <si>
+    <t>novel.1050</t>
+  </si>
+  <si>
+    <t>novel.1061</t>
+  </si>
+  <si>
+    <t>novel.1062</t>
+  </si>
+  <si>
+    <t>novel.1068</t>
+  </si>
+  <si>
+    <t>novel.1069</t>
+  </si>
+  <si>
+    <t>novel.107</t>
+  </si>
+  <si>
+    <t>novel.1071</t>
+  </si>
+  <si>
+    <t>novel.1073</t>
+  </si>
+  <si>
+    <t>novel.1074</t>
+  </si>
+  <si>
+    <t>novel.1077</t>
+  </si>
+  <si>
+    <t>novel.1078</t>
+  </si>
+  <si>
+    <t>novel.1079</t>
+  </si>
+  <si>
+    <t>novel.108</t>
+  </si>
+  <si>
+    <t>novel.1088</t>
+  </si>
+  <si>
+    <t>novel.1092</t>
+  </si>
+  <si>
+    <t>novel.1095</t>
+  </si>
+  <si>
+    <t>novel.1099</t>
+  </si>
+  <si>
+    <t>novel.11</t>
+  </si>
+  <si>
+    <t>novel.1103</t>
+  </si>
+  <si>
+    <t>novel.1105</t>
+  </si>
+  <si>
+    <t>novel.1106</t>
+  </si>
+  <si>
+    <t>novel.1107</t>
+  </si>
+  <si>
+    <t>novel.1108</t>
+  </si>
+  <si>
+    <t>novel.1110</t>
+  </si>
+  <si>
+    <t>novel.1112</t>
+  </si>
+  <si>
+    <t>novel.1113</t>
+  </si>
+  <si>
+    <t>novel.1114</t>
+  </si>
+  <si>
+    <t>novel.1124</t>
+  </si>
+  <si>
+    <t>novel.1127</t>
+  </si>
+  <si>
+    <t>novel.1130</t>
+  </si>
+  <si>
+    <t>novel.1131</t>
+  </si>
+  <si>
+    <t>novel.1136</t>
+  </si>
+  <si>
+    <t>novel.1139</t>
+  </si>
+  <si>
+    <t>novel.1142</t>
+  </si>
+  <si>
+    <t>novel.1145</t>
+  </si>
+  <si>
+    <t>novel.1146</t>
+  </si>
+  <si>
+    <t>novel.1148</t>
+  </si>
+  <si>
+    <t>novel.1149</t>
+  </si>
+  <si>
+    <t>novel.115</t>
+  </si>
+  <si>
+    <t>novel.1153</t>
+  </si>
+  <si>
+    <t>novel.1158</t>
+  </si>
+  <si>
+    <t>novel.1159</t>
+  </si>
+  <si>
+    <t>novel.116</t>
+  </si>
+  <si>
+    <t>novel.1163</t>
+  </si>
+  <si>
+    <t>novel.1167</t>
+  </si>
+  <si>
+    <t>novel.1171</t>
+  </si>
+  <si>
+    <t>novel.1172</t>
+  </si>
+  <si>
+    <t>novel.1174</t>
+  </si>
+  <si>
+    <t>novel.1175</t>
+  </si>
+  <si>
+    <t>novel.654</t>
+  </si>
+  <si>
+    <t>novel.66</t>
+  </si>
+  <si>
+    <t>novel.665</t>
+  </si>
+  <si>
+    <t>novel.669</t>
+  </si>
+  <si>
+    <t>novel.670</t>
+  </si>
+  <si>
+    <t>novel.673</t>
+  </si>
+  <si>
+    <t>novel.676</t>
+  </si>
+  <si>
+    <t>novel.677</t>
+  </si>
+  <si>
+    <t>novel.686</t>
+  </si>
+  <si>
+    <t>novel.687</t>
+  </si>
+  <si>
+    <t>novel.688</t>
+  </si>
+  <si>
+    <t>novel.693</t>
+  </si>
+  <si>
+    <t>novel.702</t>
+  </si>
+  <si>
+    <t>novel.703</t>
+  </si>
+  <si>
+    <t>novel.707</t>
+  </si>
+  <si>
+    <t>novel.710</t>
+  </si>
+  <si>
+    <t>novel.711</t>
+  </si>
+  <si>
+    <t>novel.717</t>
+  </si>
+  <si>
+    <t>novel.719</t>
+  </si>
+  <si>
+    <t>novel.722</t>
+  </si>
+  <si>
+    <t>novel.729</t>
+  </si>
+  <si>
+    <t>novel.730</t>
+  </si>
+  <si>
+    <t>novel.731</t>
+  </si>
+  <si>
+    <t>novel.739</t>
+  </si>
+  <si>
+    <t>novel.74</t>
+  </si>
+  <si>
+    <t>novel.743</t>
+  </si>
+  <si>
+    <t>novel.75</t>
+  </si>
+  <si>
+    <t>novel.756</t>
+  </si>
+  <si>
+    <t>novel.758</t>
+  </si>
+  <si>
+    <t>novel.763</t>
+  </si>
+  <si>
+    <t>novel.766</t>
+  </si>
+  <si>
+    <t>novel.77</t>
+  </si>
+  <si>
+    <t>novel.774</t>
+  </si>
+  <si>
+    <t>novel.775</t>
+  </si>
+  <si>
+    <t>novel.776</t>
+  </si>
+  <si>
+    <t>novel.778</t>
+  </si>
+  <si>
+    <t>novel.78</t>
+  </si>
+  <si>
+    <t>novel.790</t>
+  </si>
+  <si>
+    <t>novel.791</t>
+  </si>
+  <si>
+    <t>novel.796</t>
+  </si>
+  <si>
+    <t>novel.799</t>
+  </si>
+  <si>
+    <t>novel.802</t>
+  </si>
+  <si>
+    <t>novel.803</t>
+  </si>
+  <si>
+    <t>novel.804</t>
+  </si>
+  <si>
+    <t>novel.805</t>
+  </si>
+  <si>
+    <t>novel.806</t>
+  </si>
+  <si>
+    <t>novel.807</t>
+  </si>
+  <si>
+    <t>novel.808</t>
+  </si>
+  <si>
+    <t>novel.809</t>
+  </si>
+  <si>
+    <t>novel.81</t>
+  </si>
+  <si>
+    <t>novel.810</t>
+  </si>
+  <si>
+    <t>novel.812</t>
+  </si>
+  <si>
+    <t>novel.814</t>
+  </si>
+  <si>
+    <t>novel.817</t>
+  </si>
+  <si>
+    <t>novel.818</t>
+  </si>
+  <si>
+    <t>novel.82</t>
+  </si>
+  <si>
+    <t>novel.822</t>
+  </si>
+  <si>
+    <t>novel.827</t>
+  </si>
+  <si>
+    <t>novel.836</t>
+  </si>
+  <si>
+    <t>novel.850</t>
+  </si>
+  <si>
+    <t>novel.852</t>
+  </si>
+  <si>
+    <t>novel.860</t>
+  </si>
+  <si>
+    <t>novel.862</t>
+  </si>
+  <si>
+    <t>novel.866</t>
+  </si>
+  <si>
+    <t>novel.867</t>
+  </si>
+  <si>
+    <t>novel.869</t>
+  </si>
+  <si>
+    <t>novel.87</t>
+  </si>
+  <si>
+    <t>novel.872</t>
+  </si>
+  <si>
+    <t>novel.873</t>
+  </si>
+  <si>
+    <t>novel.874</t>
+  </si>
+  <si>
+    <t>novel.878</t>
+  </si>
+  <si>
+    <t>novel.879</t>
+  </si>
+  <si>
+    <t>novel.88</t>
+  </si>
+  <si>
+    <t>novel.886</t>
+  </si>
+  <si>
+    <t>novel.887</t>
+  </si>
+  <si>
+    <t>novel.888</t>
+  </si>
+  <si>
+    <t>novel.889</t>
+  </si>
+  <si>
+    <t>novel.890</t>
+  </si>
+  <si>
+    <t>novel.895</t>
+  </si>
+  <si>
+    <t>novel.896</t>
+  </si>
+  <si>
+    <t>novel.897</t>
+  </si>
+  <si>
+    <t>novel.898</t>
+  </si>
+  <si>
+    <t>novel.899</t>
+  </si>
+  <si>
+    <t>novel.9</t>
+  </si>
+  <si>
+    <t>novel.900</t>
+  </si>
+  <si>
+    <t>novel.901</t>
+  </si>
+  <si>
+    <t>novel.904</t>
+  </si>
+  <si>
+    <t>novel.905</t>
+  </si>
+  <si>
+    <t>novel.906</t>
+  </si>
+  <si>
+    <t>novel.907</t>
+  </si>
+  <si>
+    <t>novel.908</t>
+  </si>
+  <si>
+    <t>novel.909</t>
+  </si>
+  <si>
+    <t>novel.910</t>
+  </si>
+  <si>
+    <t>novel.913</t>
+  </si>
+  <si>
+    <t>novel.914</t>
+  </si>
+  <si>
+    <t>novel.915</t>
+  </si>
+  <si>
+    <t>novel.92</t>
+  </si>
+  <si>
+    <t>novel.923</t>
+  </si>
+  <si>
+    <t>novel.924</t>
+  </si>
+  <si>
+    <t>novel.928</t>
+  </si>
+  <si>
+    <t>novel.93</t>
+  </si>
+  <si>
+    <t>novel.932</t>
+  </si>
+  <si>
+    <t>novel.935</t>
+  </si>
+  <si>
+    <t>novel.936</t>
+  </si>
+  <si>
+    <t>novel.937</t>
+  </si>
+  <si>
+    <t>novel.940</t>
+  </si>
+  <si>
+    <t>novel.942</t>
+  </si>
+  <si>
+    <t>novel.95</t>
+  </si>
+  <si>
+    <t>novel.950</t>
+  </si>
+  <si>
+    <t>novel.951</t>
+  </si>
+  <si>
+    <t>novel.952</t>
+  </si>
+  <si>
+    <t>novel.96</t>
+  </si>
+  <si>
+    <t>novel.966</t>
+  </si>
+  <si>
+    <t>novel.969</t>
+  </si>
+  <si>
+    <t>novel.970</t>
+  </si>
+  <si>
+    <t>novel.971</t>
+  </si>
+  <si>
+    <t>novel.972</t>
+  </si>
+  <si>
+    <t>novel.973</t>
+  </si>
+  <si>
+    <t>novel.976</t>
+  </si>
+  <si>
+    <t>novel.977</t>
+  </si>
+  <si>
+    <t>novel.979</t>
+  </si>
+  <si>
+    <t>novel.98</t>
+  </si>
+  <si>
+    <t>novel.980</t>
+  </si>
+  <si>
+    <t>novel.983</t>
+  </si>
+  <si>
+    <t>novel.984</t>
+  </si>
+  <si>
+    <t>novel.99</t>
+  </si>
+  <si>
+    <t>novel.990</t>
+  </si>
+  <si>
+    <t>novel.991</t>
+  </si>
+  <si>
+    <t>novel.992</t>
+  </si>
+  <si>
+    <t>novel.996</t>
+  </si>
+  <si>
+    <t>NP24</t>
+  </si>
+  <si>
+    <t>NRAMP1</t>
+  </si>
+  <si>
+    <t>NRAMP3</t>
+  </si>
+  <si>
+    <t>NRT2.2</t>
+  </si>
+  <si>
+    <t>NSGT1</t>
+  </si>
+  <si>
+    <t>NSY</t>
+  </si>
+  <si>
+    <t>NXD1</t>
+  </si>
+  <si>
+    <t>OAT</t>
+  </si>
+  <si>
+    <t>ODC</t>
+  </si>
+  <si>
+    <t>ODD</t>
+  </si>
+  <si>
+    <t>OPR1</t>
+  </si>
+  <si>
+    <t>opr2</t>
+  </si>
+  <si>
+    <t>opr3</t>
+  </si>
+  <si>
+    <t>OPT1</t>
+  </si>
+  <si>
+    <t>ORFX</t>
+  </si>
+  <si>
+    <t>OTC</t>
+  </si>
+  <si>
+    <t>P18</t>
+  </si>
+  <si>
+    <t>P4</t>
+  </si>
+  <si>
+    <t>P69A</t>
+  </si>
+  <si>
+    <t>P69B</t>
+  </si>
+  <si>
+    <t>p69c</t>
+  </si>
+  <si>
+    <t>p69d</t>
+  </si>
+  <si>
+    <t>p69F</t>
+  </si>
+  <si>
+    <t>PAD1</t>
+  </si>
+  <si>
+    <t>PAL2</t>
+  </si>
+  <si>
+    <t>PAL3</t>
+  </si>
+  <si>
+    <t>PAP1</t>
+  </si>
+  <si>
+    <t>PAT</t>
+  </si>
+  <si>
+    <t>PCL1</t>
+  </si>
+  <si>
+    <t>pcna</t>
+  </si>
+  <si>
+    <t>PDF1A</t>
+  </si>
+  <si>
+    <t>PDF1B</t>
+  </si>
+  <si>
+    <t>PDH</t>
+  </si>
+  <si>
+    <t>Pdk1</t>
+  </si>
+  <si>
+    <t>pds</t>
+  </si>
+  <si>
+    <t>PE1</t>
+  </si>
+  <si>
+    <t>PELOTA</t>
+  </si>
+  <si>
+    <t>PGcat</t>
+  </si>
+  <si>
+    <t>PGH1</t>
+  </si>
+  <si>
+    <t>pglcat8</t>
+  </si>
+  <si>
+    <t>pGlcT1</t>
+  </si>
+  <si>
+    <t>pGlcT3</t>
+  </si>
+  <si>
+    <t>pGlcT4</t>
+  </si>
+  <si>
+    <t>PHOT1</t>
+  </si>
+  <si>
+    <t>PHOT2</t>
+  </si>
+  <si>
+    <t>PHS1</t>
+  </si>
+  <si>
+    <t>phyA</t>
+  </si>
+  <si>
+    <t>PHYB1</t>
+  </si>
+  <si>
+    <t>PHYB2</t>
+  </si>
+  <si>
+    <t>PHYE</t>
+  </si>
+  <si>
+    <t>PHYF</t>
+  </si>
+  <si>
+    <t>PIN10</t>
+  </si>
+  <si>
+    <t>PIN2</t>
+  </si>
+  <si>
+    <t>PIN3</t>
+  </si>
+  <si>
+    <t>PIN4</t>
+  </si>
+  <si>
+    <t>PIN5</t>
+  </si>
+  <si>
+    <t>PIN6</t>
+  </si>
+  <si>
+    <t>PIN7</t>
+  </si>
+  <si>
+    <t>PIN8</t>
+  </si>
+  <si>
+    <t>pip1</t>
+  </si>
+  <si>
+    <t>PIP1-5</t>
+  </si>
+  <si>
+    <t>PLC7</t>
+  </si>
+  <si>
+    <t>PLDa1</t>
+  </si>
+  <si>
+    <t>PLDa2</t>
+  </si>
+  <si>
+    <t>PLDb1</t>
+  </si>
+  <si>
+    <t>PLDb2</t>
+  </si>
+  <si>
+    <t>PLIM2a</t>
+  </si>
+  <si>
+    <t>PME2.1</t>
+  </si>
+  <si>
+    <t>PMEI</t>
+  </si>
+  <si>
+    <t>PMEU1</t>
+  </si>
+  <si>
+    <t>pmt</t>
+  </si>
+  <si>
+    <t>PMT5</t>
+  </si>
+  <si>
+    <t>PMT6</t>
+  </si>
+  <si>
+    <t>PP2Ac1</t>
+  </si>
+  <si>
+    <t>PP2Ac2</t>
+  </si>
+  <si>
+    <t>PP2C-1</t>
+  </si>
+  <si>
+    <t>PP2C-2</t>
+  </si>
+  <si>
+    <t>PP5</t>
+  </si>
+  <si>
+    <t>ppc2</t>
+  </si>
+  <si>
+    <t>PPCK1</t>
+  </si>
+  <si>
+    <t>PPO-2</t>
+  </si>
+  <si>
+    <t>PR-1a1</t>
+  </si>
+  <si>
+    <t>PR-P2</t>
+  </si>
+  <si>
+    <t>PR1a2</t>
+  </si>
+  <si>
+    <t>PR1b1</t>
+  </si>
+  <si>
+    <t>Prg1</t>
+  </si>
+  <si>
+    <t>PRK1</t>
+  </si>
+  <si>
+    <t>PRK2</t>
+  </si>
+  <si>
+    <t>PRK3</t>
+  </si>
+  <si>
+    <t>PRO1</t>
+  </si>
+  <si>
+    <t>PRO2</t>
+  </si>
+  <si>
+    <t>profilin</t>
+  </si>
+  <si>
+    <t>ProT1</t>
+  </si>
+  <si>
+    <t>ProT2</t>
+  </si>
+  <si>
+    <t>ProT3</t>
+  </si>
+  <si>
+    <t>PS-2</t>
+  </si>
+  <si>
+    <t>PSBR</t>
+  </si>
+  <si>
+    <t>psi14A</t>
+  </si>
+  <si>
+    <t>psi14B</t>
+  </si>
+  <si>
+    <t>PSK1</t>
+  </si>
+  <si>
+    <t>PSK2</t>
+  </si>
+  <si>
+    <t>PSK3</t>
+  </si>
+  <si>
+    <t>PSR</t>
+  </si>
+  <si>
+    <t>PSY2</t>
+  </si>
+  <si>
+    <t>PT1</t>
+  </si>
+  <si>
+    <t>PT2</t>
+  </si>
+  <si>
+    <t>LOC778303</t>
   </si>
 </sst>
 </file>
@@ -6719,6 +9041,7 @@
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -6749,13 +9072,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7059,7 +9385,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A2227"/>
+  <dimension ref="A1:A3192"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="2"/>
@@ -18200,6 +20526,4449 @@
         <v>2226</v>
       </c>
     </row>
+    <row r="2228" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2228" s="3" t="s">
+        <v>2227</v>
+      </c>
+    </row>
+    <row r="2229" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2229" s="3" t="s">
+        <v>2228</v>
+      </c>
+    </row>
+    <row r="2230" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2230" s="3" t="s">
+        <v>2229</v>
+      </c>
+    </row>
+    <row r="2231" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2231" s="3" t="s">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="2232" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2232" s="3" t="s">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="2233" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2233" s="3" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="2234" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2234" s="3" t="s">
+        <v>2233</v>
+      </c>
+    </row>
+    <row r="2235" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2235" s="3" t="s">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="2236" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2236" s="3" t="s">
+        <v>2235</v>
+      </c>
+    </row>
+    <row r="2237" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2237" s="3" t="s">
+        <v>2236</v>
+      </c>
+    </row>
+    <row r="2238" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2238" s="3" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2239" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2239" s="3" t="s">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="2240" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2240" s="3" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="2241" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2241" s="3" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="2242" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2242" s="3" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="2243" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2243" s="3" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="2244" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2244" s="3" t="s">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="2245" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2245" s="3" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="2246" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2246" s="3" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="2247" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2247" s="3" t="s">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="2248" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2248" s="3" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="2249" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2249" s="3" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="2250" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2250" s="3" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="2251" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2251" s="3" t="s">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="2252" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2252" s="3" t="s">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="2253" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2253" s="3" t="s">
+        <v>2252</v>
+      </c>
+    </row>
+    <row r="2254" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2254" s="3" t="s">
+        <v>2253</v>
+      </c>
+    </row>
+    <row r="2255" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2255" s="3" t="s">
+        <v>2254</v>
+      </c>
+    </row>
+    <row r="2256" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2256" s="3" t="s">
+        <v>2255</v>
+      </c>
+    </row>
+    <row r="2257" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2257" s="3" t="s">
+        <v>2256</v>
+      </c>
+    </row>
+    <row r="2258" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2258" s="3" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="2259" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2259" s="3" t="s">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="2260" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2260" s="3" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="2261" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2261" s="3" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="2262" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2262" s="3" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="2263" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2263" s="3" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="2264" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2264" s="3" t="s">
+        <v>2263</v>
+      </c>
+    </row>
+    <row r="2265" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2265" s="3" t="s">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="2266" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2266" s="3" t="s">
+        <v>2265</v>
+      </c>
+    </row>
+    <row r="2267" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2267" s="3" t="s">
+        <v>2266</v>
+      </c>
+    </row>
+    <row r="2268" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2268" s="3" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="2269" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2269" s="3" t="s">
+        <v>2268</v>
+      </c>
+    </row>
+    <row r="2270" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2270" s="3" t="s">
+        <v>2269</v>
+      </c>
+    </row>
+    <row r="2271" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2271" s="3" t="s">
+        <v>2270</v>
+      </c>
+    </row>
+    <row r="2272" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2272" s="3" t="s">
+        <v>2271</v>
+      </c>
+    </row>
+    <row r="2273" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2273" s="3" t="s">
+        <v>2272</v>
+      </c>
+    </row>
+    <row r="2274" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2274" s="3" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2275" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2275" s="3" t="s">
+        <v>2274</v>
+      </c>
+    </row>
+    <row r="2276" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2276" s="3" t="s">
+        <v>2275</v>
+      </c>
+    </row>
+    <row r="2277" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2277" s="3" t="s">
+        <v>2276</v>
+      </c>
+    </row>
+    <row r="2278" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2278" s="3" t="s">
+        <v>2277</v>
+      </c>
+    </row>
+    <row r="2279" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2279" s="3" t="s">
+        <v>2278</v>
+      </c>
+    </row>
+    <row r="2280" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2280" s="3" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="2281" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2281" s="3" t="s">
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="2282" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2282" s="3" t="s">
+        <v>2281</v>
+      </c>
+    </row>
+    <row r="2283" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2283" s="3" t="s">
+        <v>2282</v>
+      </c>
+    </row>
+    <row r="2284" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2284" s="3" t="s">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="2285" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2285" s="3" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="2286" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2286" s="3" t="s">
+        <v>2285</v>
+      </c>
+    </row>
+    <row r="2287" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2287" s="3" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="2288" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2288" s="3" t="s">
+        <v>2287</v>
+      </c>
+    </row>
+    <row r="2289" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2289" s="3" t="s">
+        <v>2288</v>
+      </c>
+    </row>
+    <row r="2290" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2290" s="3" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="2291" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2291" s="3" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="2292" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2292" s="3" t="s">
+        <v>2291</v>
+      </c>
+    </row>
+    <row r="2293" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2293" s="3" t="s">
+        <v>2292</v>
+      </c>
+    </row>
+    <row r="2294" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2294" s="3" t="s">
+        <v>2293</v>
+      </c>
+    </row>
+    <row r="2295" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2295" s="3" t="s">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="2296" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2296" s="3" t="s">
+        <v>2295</v>
+      </c>
+    </row>
+    <row r="2297" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2297" s="3" t="s">
+        <v>2296</v>
+      </c>
+    </row>
+    <row r="2298" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2298" s="3" t="s">
+        <v>2297</v>
+      </c>
+    </row>
+    <row r="2299" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2299" s="3" t="s">
+        <v>2298</v>
+      </c>
+    </row>
+    <row r="2300" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2300" s="3" t="s">
+        <v>2299</v>
+      </c>
+    </row>
+    <row r="2301" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2301" s="3" t="s">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="2302" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2302" s="3" t="s">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="2303" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2303" s="3" t="s">
+        <v>2302</v>
+      </c>
+    </row>
+    <row r="2304" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2304" s="3" t="s">
+        <v>2303</v>
+      </c>
+    </row>
+    <row r="2305" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2305" s="3" t="s">
+        <v>2304</v>
+      </c>
+    </row>
+    <row r="2306" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2306" s="3" t="s">
+        <v>2305</v>
+      </c>
+    </row>
+    <row r="2307" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2307" s="3" t="s">
+        <v>2306</v>
+      </c>
+    </row>
+    <row r="2308" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2308" s="3" t="s">
+        <v>2307</v>
+      </c>
+    </row>
+    <row r="2309" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2309" s="3" t="s">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="2310" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2310" s="3" t="s">
+        <v>2309</v>
+      </c>
+    </row>
+    <row r="2311" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2311" s="3" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="2312" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2312" s="3" t="s">
+        <v>2311</v>
+      </c>
+    </row>
+    <row r="2313" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2313" s="3" t="s">
+        <v>2312</v>
+      </c>
+    </row>
+    <row r="2314" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2314" s="3" t="s">
+        <v>2313</v>
+      </c>
+    </row>
+    <row r="2315" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2315" s="3" t="s">
+        <v>2314</v>
+      </c>
+    </row>
+    <row r="2316" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2316" s="3" t="s">
+        <v>2315</v>
+      </c>
+    </row>
+    <row r="2317" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2317" s="3" t="s">
+        <v>2316</v>
+      </c>
+    </row>
+    <row r="2318" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2318" s="3" t="s">
+        <v>2317</v>
+      </c>
+    </row>
+    <row r="2319" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2319" s="3" t="s">
+        <v>2318</v>
+      </c>
+    </row>
+    <row r="2320" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2320" s="3" t="s">
+        <v>2319</v>
+      </c>
+    </row>
+    <row r="2321" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2321" s="3" t="s">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="2322" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2322" s="3" t="s">
+        <v>2321</v>
+      </c>
+    </row>
+    <row r="2323" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2323" s="3" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="2324" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2324" s="3" t="s">
+        <v>2323</v>
+      </c>
+    </row>
+    <row r="2325" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2325" s="3" t="s">
+        <v>2324</v>
+      </c>
+    </row>
+    <row r="2326" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2326" s="3" t="s">
+        <v>2325</v>
+      </c>
+    </row>
+    <row r="2327" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2327" s="3" t="s">
+        <v>2326</v>
+      </c>
+    </row>
+    <row r="2328" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2328" s="3" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="2329" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2329" s="3" t="s">
+        <v>2328</v>
+      </c>
+    </row>
+    <row r="2330" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2330" s="3" t="s">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="2331" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2331" s="3" t="s">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="2332" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2332" s="3" t="s">
+        <v>2331</v>
+      </c>
+    </row>
+    <row r="2333" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2333" s="3" t="s">
+        <v>2332</v>
+      </c>
+    </row>
+    <row r="2334" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2334" s="3" t="s">
+        <v>2333</v>
+      </c>
+    </row>
+    <row r="2335" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2335" s="3" t="s">
+        <v>2334</v>
+      </c>
+    </row>
+    <row r="2336" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2336" s="3" t="s">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="2337" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2337" s="3" t="s">
+        <v>2336</v>
+      </c>
+    </row>
+    <row r="2338" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2338" s="3" t="s">
+        <v>2337</v>
+      </c>
+    </row>
+    <row r="2339" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2339" s="3" t="s">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="2340" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2340" s="3" t="s">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="2341" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2341" s="3" t="s">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="2342" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2342" s="3" t="s">
+        <v>2341</v>
+      </c>
+    </row>
+    <row r="2343" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2343" s="3" t="s">
+        <v>2342</v>
+      </c>
+    </row>
+    <row r="2344" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2344" s="3" t="s">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="2345" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2345" s="3" t="s">
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="2346" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2346" s="3" t="s">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="2347" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2347" s="3" t="s">
+        <v>2346</v>
+      </c>
+    </row>
+    <row r="2348" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2348" s="3" t="s">
+        <v>2347</v>
+      </c>
+    </row>
+    <row r="2349" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2349" s="3" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="2350" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2350" s="3" t="s">
+        <v>2349</v>
+      </c>
+    </row>
+    <row r="2351" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2351" s="3" t="s">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="2352" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2352" s="3" t="s">
+        <v>2351</v>
+      </c>
+    </row>
+    <row r="2353" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2353" s="3" t="s">
+        <v>2352</v>
+      </c>
+    </row>
+    <row r="2354" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2354" s="3" t="s">
+        <v>2353</v>
+      </c>
+    </row>
+    <row r="2355" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2355" s="3" t="s">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="2356" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2356" s="3" t="s">
+        <v>2355</v>
+      </c>
+    </row>
+    <row r="2357" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2357" s="3" t="s">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="2358" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2358" s="3" t="s">
+        <v>2357</v>
+      </c>
+    </row>
+    <row r="2359" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2359" s="3" t="s">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="2360" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2360" s="3" t="s">
+        <v>2359</v>
+      </c>
+    </row>
+    <row r="2361" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2361" s="3" t="s">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="2362" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2362" s="3" t="s">
+        <v>2361</v>
+      </c>
+    </row>
+    <row r="2363" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2363" s="3" t="s">
+        <v>2362</v>
+      </c>
+    </row>
+    <row r="2364" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2364" s="3" t="s">
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="2365" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2365" s="3" t="s">
+        <v>2364</v>
+      </c>
+    </row>
+    <row r="2366" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2366" s="3" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="2367" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2367" s="3" t="s">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="2368" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2368" s="3" t="s">
+        <v>2367</v>
+      </c>
+    </row>
+    <row r="2369" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2369" s="3" t="s">
+        <v>2368</v>
+      </c>
+    </row>
+    <row r="2370" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2370" s="3" t="s">
+        <v>2369</v>
+      </c>
+    </row>
+    <row r="2371" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2371" s="3" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="2372" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2372" s="3" t="s">
+        <v>2371</v>
+      </c>
+    </row>
+    <row r="2373" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2373" s="3" t="s">
+        <v>2372</v>
+      </c>
+    </row>
+    <row r="2374" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2374" s="3" t="s">
+        <v>2373</v>
+      </c>
+    </row>
+    <row r="2375" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2375" s="3" t="s">
+        <v>2374</v>
+      </c>
+    </row>
+    <row r="2376" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2376" s="3" t="s">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="2377" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2377" s="3" t="s">
+        <v>2376</v>
+      </c>
+    </row>
+    <row r="2378" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2378" s="3" t="s">
+        <v>2377</v>
+      </c>
+    </row>
+    <row r="2379" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2379" s="3" t="s">
+        <v>2378</v>
+      </c>
+    </row>
+    <row r="2380" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2380" s="3" t="s">
+        <v>2379</v>
+      </c>
+    </row>
+    <row r="2381" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2381" s="3" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="2382" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2382" s="3" t="s">
+        <v>2381</v>
+      </c>
+    </row>
+    <row r="2383" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2383" s="3" t="s">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="2384" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2384" s="3" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="2385" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2385" s="3" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="2386" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2386" s="3" t="s">
+        <v>2385</v>
+      </c>
+    </row>
+    <row r="2387" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2387" s="3" t="s">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="2388" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2388" s="3" t="s">
+        <v>2387</v>
+      </c>
+    </row>
+    <row r="2389" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2389" s="3" t="s">
+        <v>2388</v>
+      </c>
+    </row>
+    <row r="2390" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2390" s="3" t="s">
+        <v>2389</v>
+      </c>
+    </row>
+    <row r="2391" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2391" s="3" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="2392" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2392" s="3" t="s">
+        <v>2391</v>
+      </c>
+    </row>
+    <row r="2393" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2393" s="3" t="s">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="2394" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2394" s="3" t="s">
+        <v>2393</v>
+      </c>
+    </row>
+    <row r="2395" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2395" s="3" t="s">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="2396" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2396" s="3" t="s">
+        <v>2395</v>
+      </c>
+    </row>
+    <row r="2397" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2397" s="3" t="s">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="2398" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2398" s="3" t="s">
+        <v>2397</v>
+      </c>
+    </row>
+    <row r="2399" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2399" s="3" t="s">
+        <v>2398</v>
+      </c>
+    </row>
+    <row r="2400" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2400" s="3" t="s">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="2401" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2401" s="3" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="2402" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2402" s="3" t="s">
+        <v>2401</v>
+      </c>
+    </row>
+    <row r="2403" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2403" s="3" t="s">
+        <v>2402</v>
+      </c>
+    </row>
+    <row r="2404" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2404" s="3" t="s">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="2405" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2405" s="3" t="s">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="2406" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2406" s="3" t="s">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="2407" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2407" s="3" t="s">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="2408" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2408" s="3" t="s">
+        <v>2407</v>
+      </c>
+    </row>
+    <row r="2409" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2409" s="3" t="s">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="2410" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2410" s="3" t="s">
+        <v>2409</v>
+      </c>
+    </row>
+    <row r="2411" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2411" s="3" t="s">
+        <v>2410</v>
+      </c>
+    </row>
+    <row r="2412" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2412" s="3" t="s">
+        <v>2411</v>
+      </c>
+    </row>
+    <row r="2413" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2413" s="3" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="2414" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2414" s="3" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="2415" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2415" s="3" t="s">
+        <v>2414</v>
+      </c>
+    </row>
+    <row r="2416" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2416" s="3" t="s">
+        <v>2415</v>
+      </c>
+    </row>
+    <row r="2417" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2417" s="3" t="s">
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="2418" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2418" s="3" t="s">
+        <v>2417</v>
+      </c>
+    </row>
+    <row r="2419" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2419" s="3" t="s">
+        <v>2418</v>
+      </c>
+    </row>
+    <row r="2420" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2420" s="3" t="s">
+        <v>2419</v>
+      </c>
+    </row>
+    <row r="2421" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2421" s="3" t="s">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="2422" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2422" s="3" t="s">
+        <v>2421</v>
+      </c>
+    </row>
+    <row r="2423" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2423" s="3" t="s">
+        <v>2422</v>
+      </c>
+    </row>
+    <row r="2424" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2424" s="3" t="s">
+        <v>2423</v>
+      </c>
+    </row>
+    <row r="2425" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2425" s="3" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="2426" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2426" s="3" t="s">
+        <v>2425</v>
+      </c>
+    </row>
+    <row r="2427" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2427" s="3" t="s">
+        <v>2426</v>
+      </c>
+    </row>
+    <row r="2428" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2428" s="3" t="s">
+        <v>2427</v>
+      </c>
+    </row>
+    <row r="2429" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2429" s="3" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="2430" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2430" s="3" t="s">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="2431" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2431" s="3" t="s">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="2432" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2432" s="3" t="s">
+        <v>2431</v>
+      </c>
+    </row>
+    <row r="2433" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2433" s="3" t="s">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="2434" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2434" s="3" t="s">
+        <v>2433</v>
+      </c>
+    </row>
+    <row r="2435" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2435" s="3" t="s">
+        <v>2434</v>
+      </c>
+    </row>
+    <row r="2436" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2436" s="3" t="s">
+        <v>2435</v>
+      </c>
+    </row>
+    <row r="2437" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2437" s="3" t="s">
+        <v>2436</v>
+      </c>
+    </row>
+    <row r="2438" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2438" s="3" t="s">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="2439" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2439" s="3" t="s">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="2440" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2440" s="3" t="s">
+        <v>2439</v>
+      </c>
+    </row>
+    <row r="2441" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2441" s="3" t="s">
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="2442" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2442" s="3" t="s">
+        <v>2441</v>
+      </c>
+    </row>
+    <row r="2443" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2443" s="3" t="s">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="2444" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2444" s="3" t="s">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="2445" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2445" s="3" t="s">
+        <v>2444</v>
+      </c>
+    </row>
+    <row r="2446" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2446" s="3" t="s">
+        <v>2445</v>
+      </c>
+    </row>
+    <row r="2447" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2447" s="3" t="s">
+        <v>2446</v>
+      </c>
+    </row>
+    <row r="2448" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2448" s="3" t="s">
+        <v>2447</v>
+      </c>
+    </row>
+    <row r="2449" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2449" s="3" t="s">
+        <v>2448</v>
+      </c>
+    </row>
+    <row r="2450" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2450" s="3" t="s">
+        <v>2449</v>
+      </c>
+    </row>
+    <row r="2451" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2451" s="3" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="2452" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2452" s="3" t="s">
+        <v>2451</v>
+      </c>
+    </row>
+    <row r="2453" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2453" s="3" t="s">
+        <v>2452</v>
+      </c>
+    </row>
+    <row r="2454" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2454" s="3" t="s">
+        <v>2453</v>
+      </c>
+    </row>
+    <row r="2455" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2455" s="3" t="s">
+        <v>2454</v>
+      </c>
+    </row>
+    <row r="2456" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2456" s="3" t="s">
+        <v>2455</v>
+      </c>
+    </row>
+    <row r="2457" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2457" s="3" t="s">
+        <v>2456</v>
+      </c>
+    </row>
+    <row r="2458" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2458" s="3" t="s">
+        <v>2457</v>
+      </c>
+    </row>
+    <row r="2459" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2459" s="3" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2460" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2460" s="3" t="s">
+        <v>2459</v>
+      </c>
+    </row>
+    <row r="2461" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2461" s="3" t="s">
+        <v>2460</v>
+      </c>
+    </row>
+    <row r="2462" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2462" s="3" t="s">
+        <v>2461</v>
+      </c>
+    </row>
+    <row r="2463" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2463" s="3" t="s">
+        <v>2462</v>
+      </c>
+    </row>
+    <row r="2464" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2464" s="3" t="s">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="2465" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2465" s="3" t="s">
+        <v>2464</v>
+      </c>
+    </row>
+    <row r="2466" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2466" s="3" t="s">
+        <v>2465</v>
+      </c>
+    </row>
+    <row r="2467" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2467" s="3" t="s">
+        <v>2466</v>
+      </c>
+    </row>
+    <row r="2468" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2468" s="3" t="s">
+        <v>2467</v>
+      </c>
+    </row>
+    <row r="2469" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2469" s="3" t="s">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="2470" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2470" s="3" t="s">
+        <v>2469</v>
+      </c>
+    </row>
+    <row r="2471" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2471" s="3" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="2472" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2472" s="3" t="s">
+        <v>2471</v>
+      </c>
+    </row>
+    <row r="2473" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2473" s="3" t="s">
+        <v>2472</v>
+      </c>
+    </row>
+    <row r="2474" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2474" s="3" t="s">
+        <v>2473</v>
+      </c>
+    </row>
+    <row r="2475" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2475" s="3" t="s">
+        <v>2474</v>
+      </c>
+    </row>
+    <row r="2476" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2476" s="3" t="s">
+        <v>2475</v>
+      </c>
+    </row>
+    <row r="2477" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2477" s="3" t="s">
+        <v>2476</v>
+      </c>
+    </row>
+    <row r="2478" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2478" s="3" t="s">
+        <v>2477</v>
+      </c>
+    </row>
+    <row r="2479" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2479" s="3" t="s">
+        <v>2478</v>
+      </c>
+    </row>
+    <row r="2480" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2480" s="3" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="2481" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2481" s="3" t="s">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="2482" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2482" s="3" t="s">
+        <v>2481</v>
+      </c>
+    </row>
+    <row r="2483" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2483" s="3" t="s">
+        <v>2482</v>
+      </c>
+    </row>
+    <row r="2484" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2484" s="3" t="s">
+        <v>2483</v>
+      </c>
+    </row>
+    <row r="2485" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2485" s="3" t="s">
+        <v>2484</v>
+      </c>
+    </row>
+    <row r="2486" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2486" s="3" t="s">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="2487" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2487" s="3" t="s">
+        <v>2486</v>
+      </c>
+    </row>
+    <row r="2488" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2488" s="3" t="s">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="2489" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2489" s="3" t="s">
+        <v>2488</v>
+      </c>
+    </row>
+    <row r="2490" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2490" s="3" t="s">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="2491" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2491" s="3" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="2492" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2492" s="3" t="s">
+        <v>2491</v>
+      </c>
+    </row>
+    <row r="2493" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2493" s="3" t="s">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="2494" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2494" s="3" t="s">
+        <v>2493</v>
+      </c>
+    </row>
+    <row r="2495" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2495" s="3" t="s">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="2496" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2496" s="3" t="s">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="2497" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2497" s="3" t="s">
+        <v>2496</v>
+      </c>
+    </row>
+    <row r="2498" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2498" s="3" t="s">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="2499" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2499" s="3" t="s">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="2500" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2500" s="3" t="s">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="2501" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2501" s="3" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="2502" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2502" s="3" t="s">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="2503" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2503" s="3" t="s">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="2504" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2504" s="3" t="s">
+        <v>2503</v>
+      </c>
+    </row>
+    <row r="2505" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2505" s="3" t="s">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="2506" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2506" s="3" t="s">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="2507" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2507" s="3" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="2508" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2508" s="3" t="s">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="2509" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2509" s="3" t="s">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="2510" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2510" s="3" t="s">
+        <v>2509</v>
+      </c>
+    </row>
+    <row r="2511" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2511" s="3" t="s">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="2512" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2512" s="3" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="2513" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2513" s="3" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="2514" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2514" s="3" t="s">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="2515" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2515" s="3" t="s">
+        <v>2514</v>
+      </c>
+    </row>
+    <row r="2516" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2516" s="3" t="s">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="2517" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2517" s="3" t="s">
+        <v>2516</v>
+      </c>
+    </row>
+    <row r="2518" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2518" s="3" t="s">
+        <v>2517</v>
+      </c>
+    </row>
+    <row r="2519" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2519" s="3" t="s">
+        <v>2518</v>
+      </c>
+    </row>
+    <row r="2520" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2520" s="3" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="2521" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2521" s="3" t="s">
+        <v>2520</v>
+      </c>
+    </row>
+    <row r="2522" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2522" s="3" t="s">
+        <v>2521</v>
+      </c>
+    </row>
+    <row r="2523" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2523" s="3" t="s">
+        <v>2522</v>
+      </c>
+    </row>
+    <row r="2524" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2524" s="3" t="s">
+        <v>2523</v>
+      </c>
+    </row>
+    <row r="2525" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2525" s="3" t="s">
+        <v>2524</v>
+      </c>
+    </row>
+    <row r="2526" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2526" s="3" t="s">
+        <v>2525</v>
+      </c>
+    </row>
+    <row r="2527" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2527" s="3" t="s">
+        <v>2526</v>
+      </c>
+    </row>
+    <row r="2528" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2528" s="3" t="s">
+        <v>2527</v>
+      </c>
+    </row>
+    <row r="2529" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2529" s="3" t="s">
+        <v>2528</v>
+      </c>
+    </row>
+    <row r="2530" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2530" s="3" t="s">
+        <v>2529</v>
+      </c>
+    </row>
+    <row r="2531" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2531" s="3" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2532" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2532" s="3" t="s">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="2533" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2533" s="3" t="s">
+        <v>2532</v>
+      </c>
+    </row>
+    <row r="2534" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2534" s="3" t="s">
+        <v>2533</v>
+      </c>
+    </row>
+    <row r="2535" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2535" s="3" t="s">
+        <v>2534</v>
+      </c>
+    </row>
+    <row r="2536" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2536" s="3" t="s">
+        <v>2535</v>
+      </c>
+    </row>
+    <row r="2537" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2537" s="3" t="s">
+        <v>2536</v>
+      </c>
+    </row>
+    <row r="2538" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2538" s="3" t="s">
+        <v>2537</v>
+      </c>
+    </row>
+    <row r="2539" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2539" s="3" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="2540" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2540" s="3" t="s">
+        <v>2539</v>
+      </c>
+    </row>
+    <row r="2541" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2541" s="3" t="s">
+        <v>2540</v>
+      </c>
+    </row>
+    <row r="2542" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2542" s="3" t="s">
+        <v>2541</v>
+      </c>
+    </row>
+    <row r="2543" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2543" s="3" t="s">
+        <v>2542</v>
+      </c>
+    </row>
+    <row r="2544" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2544" s="3" t="s">
+        <v>2543</v>
+      </c>
+    </row>
+    <row r="2545" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2545" s="3" t="s">
+        <v>2544</v>
+      </c>
+    </row>
+    <row r="2546" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2546" s="3" t="s">
+        <v>2545</v>
+      </c>
+    </row>
+    <row r="2547" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2547" s="3" t="s">
+        <v>2546</v>
+      </c>
+    </row>
+    <row r="2548" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2548" s="3" t="s">
+        <v>2547</v>
+      </c>
+    </row>
+    <row r="2549" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2549" s="3" t="s">
+        <v>2548</v>
+      </c>
+    </row>
+    <row r="2550" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2550" s="3" t="s">
+        <v>2549</v>
+      </c>
+    </row>
+    <row r="2551" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2551" s="3" t="s">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="2552" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2552" s="3" t="s">
+        <v>2551</v>
+      </c>
+    </row>
+    <row r="2553" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2553" s="3" t="s">
+        <v>2552</v>
+      </c>
+    </row>
+    <row r="2554" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2554" s="3" t="s">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="2555" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2555" s="3" t="s">
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="2556" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2556" s="3" t="s">
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="2557" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2557" s="3" t="s">
+        <v>2556</v>
+      </c>
+    </row>
+    <row r="2558" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2558" s="3" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="2559" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2559" s="3" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="2560" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2560" s="3" t="s">
+        <v>2559</v>
+      </c>
+    </row>
+    <row r="2561" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2561" s="3" t="s">
+        <v>2560</v>
+      </c>
+    </row>
+    <row r="2562" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2562" s="3" t="s">
+        <v>2561</v>
+      </c>
+    </row>
+    <row r="2563" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2563" s="3" t="s">
+        <v>2562</v>
+      </c>
+    </row>
+    <row r="2564" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2564" s="3" t="s">
+        <v>2563</v>
+      </c>
+    </row>
+    <row r="2565" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2565" s="3" t="s">
+        <v>2564</v>
+      </c>
+    </row>
+    <row r="2566" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2566" s="3" t="s">
+        <v>2565</v>
+      </c>
+    </row>
+    <row r="2567" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2567" s="3" t="s">
+        <v>2566</v>
+      </c>
+    </row>
+    <row r="2568" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2568" s="3" t="s">
+        <v>2567</v>
+      </c>
+    </row>
+    <row r="2569" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2569" s="3" t="s">
+        <v>2568</v>
+      </c>
+    </row>
+    <row r="2570" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2570" s="3" t="s">
+        <v>2569</v>
+      </c>
+    </row>
+    <row r="2571" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2571" s="3" t="s">
+        <v>2570</v>
+      </c>
+    </row>
+    <row r="2572" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2572" s="3" t="s">
+        <v>2571</v>
+      </c>
+    </row>
+    <row r="2573" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2573" s="3" t="s">
+        <v>2572</v>
+      </c>
+    </row>
+    <row r="2574" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2574" s="3" t="s">
+        <v>2573</v>
+      </c>
+    </row>
+    <row r="2575" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2575" s="3" t="s">
+        <v>2574</v>
+      </c>
+    </row>
+    <row r="2576" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2576" s="3" t="s">
+        <v>2575</v>
+      </c>
+    </row>
+    <row r="2577" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2577" s="3" t="s">
+        <v>2576</v>
+      </c>
+    </row>
+    <row r="2578" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2578" s="3" t="s">
+        <v>2577</v>
+      </c>
+    </row>
+    <row r="2579" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2579" s="3" t="s">
+        <v>2578</v>
+      </c>
+    </row>
+    <row r="2580" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2580" s="3" t="s">
+        <v>2579</v>
+      </c>
+    </row>
+    <row r="2581" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2581" s="3" t="s">
+        <v>2580</v>
+      </c>
+    </row>
+    <row r="2582" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2582" s="3" t="s">
+        <v>2581</v>
+      </c>
+    </row>
+    <row r="2583" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2583" s="3" t="s">
+        <v>2582</v>
+      </c>
+    </row>
+    <row r="2584" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2584" s="3" t="s">
+        <v>2583</v>
+      </c>
+    </row>
+    <row r="2585" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2585" s="3" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="2586" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2586" s="3" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="2587" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2587" s="3" t="s">
+        <v>2586</v>
+      </c>
+    </row>
+    <row r="2588" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2588" s="3" t="s">
+        <v>2587</v>
+      </c>
+    </row>
+    <row r="2589" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2589" s="3" t="s">
+        <v>2588</v>
+      </c>
+    </row>
+    <row r="2590" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2590" s="3" t="s">
+        <v>2589</v>
+      </c>
+    </row>
+    <row r="2591" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2591" s="3" t="s">
+        <v>2590</v>
+      </c>
+    </row>
+    <row r="2592" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2592" s="3" t="s">
+        <v>2591</v>
+      </c>
+    </row>
+    <row r="2593" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2593" s="3" t="s">
+        <v>2592</v>
+      </c>
+    </row>
+    <row r="2594" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2594" s="3" t="s">
+        <v>2593</v>
+      </c>
+    </row>
+    <row r="2595" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2595" s="3" t="s">
+        <v>2594</v>
+      </c>
+    </row>
+    <row r="2596" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2596" s="3" t="s">
+        <v>2595</v>
+      </c>
+    </row>
+    <row r="2597" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2597" s="3" t="s">
+        <v>2596</v>
+      </c>
+    </row>
+    <row r="2598" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2598" s="3" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="2599" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2599" s="3" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="2600" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2600" s="3" t="s">
+        <v>2599</v>
+      </c>
+    </row>
+    <row r="2601" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2601" s="3" t="s">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="2602" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2602" s="3" t="s">
+        <v>2601</v>
+      </c>
+    </row>
+    <row r="2603" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2603" s="3" t="s">
+        <v>2602</v>
+      </c>
+    </row>
+    <row r="2604" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2604" s="3" t="s">
+        <v>2603</v>
+      </c>
+    </row>
+    <row r="2605" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2605" s="3" t="s">
+        <v>2604</v>
+      </c>
+    </row>
+    <row r="2606" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2606" s="3" t="s">
+        <v>2605</v>
+      </c>
+    </row>
+    <row r="2607" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2607" s="3" t="s">
+        <v>2606</v>
+      </c>
+    </row>
+    <row r="2608" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2608" s="3" t="s">
+        <v>2607</v>
+      </c>
+    </row>
+    <row r="2609" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2609" s="3" t="s">
+        <v>2608</v>
+      </c>
+    </row>
+    <row r="2610" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2610" s="3" t="s">
+        <v>2609</v>
+      </c>
+    </row>
+    <row r="2611" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2611" s="3" t="s">
+        <v>2610</v>
+      </c>
+    </row>
+    <row r="2612" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2612" s="3" t="s">
+        <v>2611</v>
+      </c>
+    </row>
+    <row r="2613" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2613" s="3" t="s">
+        <v>2612</v>
+      </c>
+    </row>
+    <row r="2614" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2614" s="3" t="s">
+        <v>2613</v>
+      </c>
+    </row>
+    <row r="2615" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2615" s="3" t="s">
+        <v>2614</v>
+      </c>
+    </row>
+    <row r="2616" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2616" s="3" t="s">
+        <v>2615</v>
+      </c>
+    </row>
+    <row r="2617" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2617" s="3" t="s">
+        <v>2616</v>
+      </c>
+    </row>
+    <row r="2618" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2618" s="3" t="s">
+        <v>2617</v>
+      </c>
+    </row>
+    <row r="2619" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2619" s="3" t="s">
+        <v>2618</v>
+      </c>
+    </row>
+    <row r="2620" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2620" s="3" t="s">
+        <v>2619</v>
+      </c>
+    </row>
+    <row r="2621" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2621" s="3" t="s">
+        <v>2620</v>
+      </c>
+    </row>
+    <row r="2622" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2622" s="3" t="s">
+        <v>2621</v>
+      </c>
+    </row>
+    <row r="2623" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2623" s="3" t="s">
+        <v>2622</v>
+      </c>
+    </row>
+    <row r="2624" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2624" s="3" t="s">
+        <v>2623</v>
+      </c>
+    </row>
+    <row r="2625" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2625" s="3" t="s">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="2626" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2626" s="3" t="s">
+        <v>2625</v>
+      </c>
+    </row>
+    <row r="2627" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2627" s="3" t="s">
+        <v>2626</v>
+      </c>
+    </row>
+    <row r="2628" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2628" s="3" t="s">
+        <v>2627</v>
+      </c>
+    </row>
+    <row r="2629" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2629" s="3" t="s">
+        <v>2628</v>
+      </c>
+    </row>
+    <row r="2630" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2630" s="3" t="s">
+        <v>2629</v>
+      </c>
+    </row>
+    <row r="2631" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2631" s="3" t="s">
+        <v>2630</v>
+      </c>
+    </row>
+    <row r="2632" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2632" s="3" t="s">
+        <v>2631</v>
+      </c>
+    </row>
+    <row r="2633" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2633" s="3" t="s">
+        <v>2632</v>
+      </c>
+    </row>
+    <row r="2634" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2634" s="3" t="s">
+        <v>2633</v>
+      </c>
+    </row>
+    <row r="2635" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2635" s="3" t="s">
+        <v>2634</v>
+      </c>
+    </row>
+    <row r="2636" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2636" s="3" t="s">
+        <v>2635</v>
+      </c>
+    </row>
+    <row r="2637" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2637" s="3" t="s">
+        <v>2636</v>
+      </c>
+    </row>
+    <row r="2638" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2638" s="3" t="s">
+        <v>2637</v>
+      </c>
+    </row>
+    <row r="2639" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2639" s="3" t="s">
+        <v>2638</v>
+      </c>
+    </row>
+    <row r="2640" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2640" s="3" t="s">
+        <v>2639</v>
+      </c>
+    </row>
+    <row r="2641" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2641" s="3" t="s">
+        <v>2640</v>
+      </c>
+    </row>
+    <row r="2642" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2642" s="3" t="s">
+        <v>2641</v>
+      </c>
+    </row>
+    <row r="2643" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2643" s="3" t="s">
+        <v>2642</v>
+      </c>
+    </row>
+    <row r="2644" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2644" s="3" t="s">
+        <v>2643</v>
+      </c>
+    </row>
+    <row r="2645" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2645" s="3" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="2646" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2646" s="3" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="2647" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2647" s="3" t="s">
+        <v>2646</v>
+      </c>
+    </row>
+    <row r="2648" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2648" s="3" t="s">
+        <v>2647</v>
+      </c>
+    </row>
+    <row r="2649" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2649" s="3" t="s">
+        <v>2648</v>
+      </c>
+    </row>
+    <row r="2650" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2650" s="3" t="s">
+        <v>2649</v>
+      </c>
+    </row>
+    <row r="2651" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2651" s="3" t="s">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="2652" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2652" s="3" t="s">
+        <v>2651</v>
+      </c>
+    </row>
+    <row r="2653" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2653" s="3" t="s">
+        <v>2652</v>
+      </c>
+    </row>
+    <row r="2654" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2654" s="3" t="s">
+        <v>2653</v>
+      </c>
+    </row>
+    <row r="2655" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2655" s="3" t="s">
+        <v>2654</v>
+      </c>
+    </row>
+    <row r="2656" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2656" s="3" t="s">
+        <v>2655</v>
+      </c>
+    </row>
+    <row r="2657" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2657" s="3" t="s">
+        <v>2656</v>
+      </c>
+    </row>
+    <row r="2658" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2658" s="3" t="s">
+        <v>2657</v>
+      </c>
+    </row>
+    <row r="2659" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2659" s="3" t="s">
+        <v>2658</v>
+      </c>
+    </row>
+    <row r="2660" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2660" s="3" t="s">
+        <v>2659</v>
+      </c>
+    </row>
+    <row r="2661" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2661" s="3" t="s">
+        <v>2660</v>
+      </c>
+    </row>
+    <row r="2662" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2662" s="3" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="2663" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2663" s="3" t="s">
+        <v>2662</v>
+      </c>
+    </row>
+    <row r="2664" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2664" s="3" t="s">
+        <v>2663</v>
+      </c>
+    </row>
+    <row r="2665" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2665" s="3" t="s">
+        <v>2664</v>
+      </c>
+    </row>
+    <row r="2666" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2666" s="3" t="s">
+        <v>2665</v>
+      </c>
+    </row>
+    <row r="2667" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2667" s="3" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="2668" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2668" s="3" t="s">
+        <v>2667</v>
+      </c>
+    </row>
+    <row r="2669" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2669" s="3" t="s">
+        <v>2668</v>
+      </c>
+    </row>
+    <row r="2670" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2670" s="3" t="s">
+        <v>2669</v>
+      </c>
+    </row>
+    <row r="2671" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2671" s="3" t="s">
+        <v>2670</v>
+      </c>
+    </row>
+    <row r="2672" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2672" s="3" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="2673" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2673" s="3" t="s">
+        <v>2672</v>
+      </c>
+    </row>
+    <row r="2674" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2674" s="3" t="s">
+        <v>2673</v>
+      </c>
+    </row>
+    <row r="2675" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2675" s="3" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="2676" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2676" s="3" t="s">
+        <v>2675</v>
+      </c>
+    </row>
+    <row r="2677" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2677" s="3" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="2678" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2678" s="3" t="s">
+        <v>2677</v>
+      </c>
+    </row>
+    <row r="2679" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2679" s="3" t="s">
+        <v>2678</v>
+      </c>
+    </row>
+    <row r="2680" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2680" s="3" t="s">
+        <v>2679</v>
+      </c>
+    </row>
+    <row r="2681" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2681" s="3" t="s">
+        <v>2680</v>
+      </c>
+    </row>
+    <row r="2682" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2682" s="3" t="s">
+        <v>2681</v>
+      </c>
+    </row>
+    <row r="2683" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2683" s="3" t="s">
+        <v>2682</v>
+      </c>
+    </row>
+    <row r="2684" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2684" s="3" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="2685" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2685" s="3" t="s">
+        <v>2684</v>
+      </c>
+    </row>
+    <row r="2686" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2686" s="3" t="s">
+        <v>2685</v>
+      </c>
+    </row>
+    <row r="2687" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2687" s="3" t="s">
+        <v>2686</v>
+      </c>
+    </row>
+    <row r="2688" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2688" s="3" t="s">
+        <v>2687</v>
+      </c>
+    </row>
+    <row r="2689" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2689" s="3" t="s">
+        <v>2688</v>
+      </c>
+    </row>
+    <row r="2690" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2690" s="3" t="s">
+        <v>2689</v>
+      </c>
+    </row>
+    <row r="2691" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2691" s="3" t="s">
+        <v>2690</v>
+      </c>
+    </row>
+    <row r="2692" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2692" s="3" t="s">
+        <v>2691</v>
+      </c>
+    </row>
+    <row r="2693" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2693" s="3" t="s">
+        <v>2692</v>
+      </c>
+    </row>
+    <row r="2694" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2694" s="3" t="s">
+        <v>2693</v>
+      </c>
+    </row>
+    <row r="2695" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2695" s="3" t="s">
+        <v>2694</v>
+      </c>
+    </row>
+    <row r="2696" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2696" s="3" t="s">
+        <v>2695</v>
+      </c>
+    </row>
+    <row r="2697" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2697" s="3" t="s">
+        <v>2696</v>
+      </c>
+    </row>
+    <row r="2698" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2698" s="3" t="s">
+        <v>2697</v>
+      </c>
+    </row>
+    <row r="2699" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2699" s="3" t="s">
+        <v>2698</v>
+      </c>
+    </row>
+    <row r="2700" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2700" s="3" t="s">
+        <v>2699</v>
+      </c>
+    </row>
+    <row r="2701" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2701" s="3" t="s">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="2702" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2702" s="3" t="s">
+        <v>2701</v>
+      </c>
+    </row>
+    <row r="2703" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2703" s="3" t="s">
+        <v>2702</v>
+      </c>
+    </row>
+    <row r="2704" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2704" s="3" t="s">
+        <v>2703</v>
+      </c>
+    </row>
+    <row r="2705" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2705" s="3" t="s">
+        <v>2704</v>
+      </c>
+    </row>
+    <row r="2706" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2706" s="3" t="s">
+        <v>2705</v>
+      </c>
+    </row>
+    <row r="2707" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2707" s="3" t="s">
+        <v>2706</v>
+      </c>
+    </row>
+    <row r="2708" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2708" s="3" t="s">
+        <v>2707</v>
+      </c>
+    </row>
+    <row r="2709" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2709" s="3" t="s">
+        <v>2708</v>
+      </c>
+    </row>
+    <row r="2710" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2710" s="3" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="2711" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2711" s="3" t="s">
+        <v>2710</v>
+      </c>
+    </row>
+    <row r="2712" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2712" s="3" t="s">
+        <v>2711</v>
+      </c>
+    </row>
+    <row r="2713" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2713" s="3" t="s">
+        <v>2712</v>
+      </c>
+    </row>
+    <row r="2714" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2714" s="3" t="s">
+        <v>2713</v>
+      </c>
+    </row>
+    <row r="2715" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2715" s="3" t="s">
+        <v>2714</v>
+      </c>
+    </row>
+    <row r="2716" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2716" s="3" t="s">
+        <v>2715</v>
+      </c>
+    </row>
+    <row r="2717" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2717" s="3" t="s">
+        <v>2716</v>
+      </c>
+    </row>
+    <row r="2718" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2718" s="3" t="s">
+        <v>2717</v>
+      </c>
+    </row>
+    <row r="2719" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2719" s="3" t="s">
+        <v>2718</v>
+      </c>
+    </row>
+    <row r="2720" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2720" s="3" t="s">
+        <v>2719</v>
+      </c>
+    </row>
+    <row r="2721" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2721" s="3" t="s">
+        <v>2720</v>
+      </c>
+    </row>
+    <row r="2722" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2722" s="3" t="s">
+        <v>2721</v>
+      </c>
+    </row>
+    <row r="2723" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2723" s="3" t="s">
+        <v>2722</v>
+      </c>
+    </row>
+    <row r="2724" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2724" s="3" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="2725" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2725" s="3" t="s">
+        <v>2724</v>
+      </c>
+    </row>
+    <row r="2726" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2726" s="3" t="s">
+        <v>2725</v>
+      </c>
+    </row>
+    <row r="2727" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2727" s="3" t="s">
+        <v>2726</v>
+      </c>
+    </row>
+    <row r="2728" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2728" s="3" t="s">
+        <v>2727</v>
+      </c>
+    </row>
+    <row r="2729" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2729" s="3" t="s">
+        <v>2728</v>
+      </c>
+    </row>
+    <row r="2730" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2730" s="3" t="s">
+        <v>2729</v>
+      </c>
+    </row>
+    <row r="2731" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2731" s="3" t="s">
+        <v>2730</v>
+      </c>
+    </row>
+    <row r="2732" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2732" s="3" t="s">
+        <v>2731</v>
+      </c>
+    </row>
+    <row r="2733" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2733" s="3" t="s">
+        <v>2732</v>
+      </c>
+    </row>
+    <row r="2734" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2734" s="3" t="s">
+        <v>2733</v>
+      </c>
+    </row>
+    <row r="2735" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2735" s="3" t="s">
+        <v>2734</v>
+      </c>
+    </row>
+    <row r="2736" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2736" s="3" t="s">
+        <v>2735</v>
+      </c>
+    </row>
+    <row r="2737" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2737" s="3" t="s">
+        <v>2736</v>
+      </c>
+    </row>
+    <row r="2738" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2738" s="3" t="s">
+        <v>2737</v>
+      </c>
+    </row>
+    <row r="2739" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2739" s="3" t="s">
+        <v>2738</v>
+      </c>
+    </row>
+    <row r="2740" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2740" s="3" t="s">
+        <v>2739</v>
+      </c>
+    </row>
+    <row r="2741" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2741" s="3" t="s">
+        <v>2740</v>
+      </c>
+    </row>
+    <row r="2742" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2742" s="3" t="s">
+        <v>2741</v>
+      </c>
+    </row>
+    <row r="2743" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2743" s="3" t="s">
+        <v>2742</v>
+      </c>
+    </row>
+    <row r="2744" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2744" s="3" t="s">
+        <v>2743</v>
+      </c>
+    </row>
+    <row r="2745" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2745" s="3" t="s">
+        <v>2744</v>
+      </c>
+    </row>
+    <row r="2746" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2746" s="3" t="s">
+        <v>2745</v>
+      </c>
+    </row>
+    <row r="2747" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2747" s="3" t="s">
+        <v>2746</v>
+      </c>
+    </row>
+    <row r="2748" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2748" s="3" t="s">
+        <v>2747</v>
+      </c>
+    </row>
+    <row r="2749" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2749" s="3" t="s">
+        <v>2748</v>
+      </c>
+    </row>
+    <row r="2750" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2750" s="3" t="s">
+        <v>2749</v>
+      </c>
+    </row>
+    <row r="2751" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2751" s="3" t="s">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="2752" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2752" s="3" t="s">
+        <v>2751</v>
+      </c>
+    </row>
+    <row r="2753" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2753" s="3" t="s">
+        <v>2752</v>
+      </c>
+    </row>
+    <row r="2754" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2754" s="3" t="s">
+        <v>2753</v>
+      </c>
+    </row>
+    <row r="2755" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2755" s="3" t="s">
+        <v>2754</v>
+      </c>
+    </row>
+    <row r="2756" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2756" s="3" t="s">
+        <v>2755</v>
+      </c>
+    </row>
+    <row r="2757" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2757" s="3" t="s">
+        <v>2756</v>
+      </c>
+    </row>
+    <row r="2758" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2758" s="3" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="2759" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2759" s="3" t="s">
+        <v>2758</v>
+      </c>
+    </row>
+    <row r="2760" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2760" s="3" t="s">
+        <v>2759</v>
+      </c>
+    </row>
+    <row r="2761" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2761" s="3" t="s">
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="2762" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2762" s="3" t="s">
+        <v>2761</v>
+      </c>
+    </row>
+    <row r="2763" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2763" s="3" t="s">
+        <v>2762</v>
+      </c>
+    </row>
+    <row r="2764" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2764" s="3" t="s">
+        <v>2763</v>
+      </c>
+    </row>
+    <row r="2765" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2765" s="3" t="s">
+        <v>2764</v>
+      </c>
+    </row>
+    <row r="2766" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2766" s="3" t="s">
+        <v>2765</v>
+      </c>
+    </row>
+    <row r="2767" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2767" s="3" t="s">
+        <v>2766</v>
+      </c>
+    </row>
+    <row r="2768" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2768" s="3" t="s">
+        <v>2767</v>
+      </c>
+    </row>
+    <row r="2769" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2769" s="3" t="s">
+        <v>2768</v>
+      </c>
+    </row>
+    <row r="2770" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2770" s="3" t="s">
+        <v>2769</v>
+      </c>
+    </row>
+    <row r="2771" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2771" s="3" t="s">
+        <v>2770</v>
+      </c>
+    </row>
+    <row r="2772" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2772" s="3" t="s">
+        <v>2771</v>
+      </c>
+    </row>
+    <row r="2773" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2773" s="3" t="s">
+        <v>2772</v>
+      </c>
+    </row>
+    <row r="2774" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2774" s="3" t="s">
+        <v>2773</v>
+      </c>
+    </row>
+    <row r="2775" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2775" s="3" t="s">
+        <v>2774</v>
+      </c>
+    </row>
+    <row r="2776" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2776" s="3" t="s">
+        <v>2775</v>
+      </c>
+    </row>
+    <row r="2777" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2777" s="3" t="s">
+        <v>2776</v>
+      </c>
+    </row>
+    <row r="2778" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2778" s="3" t="s">
+        <v>2777</v>
+      </c>
+    </row>
+    <row r="2779" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2779" s="3" t="s">
+        <v>2778</v>
+      </c>
+    </row>
+    <row r="2780" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2780" s="3" t="s">
+        <v>2779</v>
+      </c>
+    </row>
+    <row r="2781" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2781" s="3" t="s">
+        <v>2780</v>
+      </c>
+    </row>
+    <row r="2782" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2782" s="3" t="s">
+        <v>2781</v>
+      </c>
+    </row>
+    <row r="2783" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2783" s="3" t="s">
+        <v>2782</v>
+      </c>
+    </row>
+    <row r="2784" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2784" s="3" t="s">
+        <v>2783</v>
+      </c>
+    </row>
+    <row r="2785" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2785" s="3" t="s">
+        <v>2784</v>
+      </c>
+    </row>
+    <row r="2786" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2786" s="3" t="s">
+        <v>2785</v>
+      </c>
+    </row>
+    <row r="2787" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2787" s="3" t="s">
+        <v>2786</v>
+      </c>
+    </row>
+    <row r="2788" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2788" s="3" t="s">
+        <v>2787</v>
+      </c>
+    </row>
+    <row r="2789" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2789" s="3" t="s">
+        <v>2788</v>
+      </c>
+    </row>
+    <row r="2790" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2790" s="3" t="s">
+        <v>2789</v>
+      </c>
+    </row>
+    <row r="2791" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2791" s="3" t="s">
+        <v>2790</v>
+      </c>
+    </row>
+    <row r="2792" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2792" s="3" t="s">
+        <v>2791</v>
+      </c>
+    </row>
+    <row r="2793" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2793" s="3" t="s">
+        <v>2792</v>
+      </c>
+    </row>
+    <row r="2794" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2794" s="3" t="s">
+        <v>2793</v>
+      </c>
+    </row>
+    <row r="2795" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2795" s="3" t="s">
+        <v>2794</v>
+      </c>
+    </row>
+    <row r="2796" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2796" s="3" t="s">
+        <v>2795</v>
+      </c>
+    </row>
+    <row r="2797" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2797" s="3" t="s">
+        <v>2796</v>
+      </c>
+    </row>
+    <row r="2798" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2798" s="3" t="s">
+        <v>2797</v>
+      </c>
+    </row>
+    <row r="2799" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2799" s="3" t="s">
+        <v>2798</v>
+      </c>
+    </row>
+    <row r="2800" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2800" s="3" t="s">
+        <v>2799</v>
+      </c>
+    </row>
+    <row r="2801" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2801" s="3" t="s">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="2802" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2802" s="3" t="s">
+        <v>2801</v>
+      </c>
+    </row>
+    <row r="2803" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2803" s="3" t="s">
+        <v>2802</v>
+      </c>
+    </row>
+    <row r="2804" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2804" s="3" t="s">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="2805" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2805" s="3" t="s">
+        <v>2804</v>
+      </c>
+    </row>
+    <row r="2806" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2806" s="3" t="s">
+        <v>2805</v>
+      </c>
+    </row>
+    <row r="2807" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2807" s="3" t="s">
+        <v>2806</v>
+      </c>
+    </row>
+    <row r="2808" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2808" s="3" t="s">
+        <v>2807</v>
+      </c>
+    </row>
+    <row r="2809" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2809" s="3" t="s">
+        <v>2808</v>
+      </c>
+    </row>
+    <row r="2810" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2810" s="3" t="s">
+        <v>2809</v>
+      </c>
+    </row>
+    <row r="2811" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2811" s="3" t="s">
+        <v>2810</v>
+      </c>
+    </row>
+    <row r="2812" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2812" s="3" t="s">
+        <v>2811</v>
+      </c>
+    </row>
+    <row r="2813" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2813" s="3" t="s">
+        <v>2812</v>
+      </c>
+    </row>
+    <row r="2814" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2814" s="3" t="s">
+        <v>2813</v>
+      </c>
+    </row>
+    <row r="2815" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2815" s="3" t="s">
+        <v>2814</v>
+      </c>
+    </row>
+    <row r="2816" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2816" s="3" t="s">
+        <v>2815</v>
+      </c>
+    </row>
+    <row r="2817" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2817" s="3" t="s">
+        <v>2816</v>
+      </c>
+    </row>
+    <row r="2818" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2818" s="3" t="s">
+        <v>2817</v>
+      </c>
+    </row>
+    <row r="2819" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2819" s="3" t="s">
+        <v>2818</v>
+      </c>
+    </row>
+    <row r="2820" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2820" s="3" t="s">
+        <v>2819</v>
+      </c>
+    </row>
+    <row r="2821" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2821" s="3" t="s">
+        <v>2820</v>
+      </c>
+    </row>
+    <row r="2822" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2822" s="3" t="s">
+        <v>2821</v>
+      </c>
+    </row>
+    <row r="2823" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2823" s="3" t="s">
+        <v>2822</v>
+      </c>
+    </row>
+    <row r="2824" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2824" s="3" t="s">
+        <v>2823</v>
+      </c>
+    </row>
+    <row r="2825" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2825" s="3" t="s">
+        <v>2824</v>
+      </c>
+    </row>
+    <row r="2826" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2826" s="3" t="s">
+        <v>2825</v>
+      </c>
+    </row>
+    <row r="2827" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2827" s="3" t="s">
+        <v>2826</v>
+      </c>
+    </row>
+    <row r="2828" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2828" s="3" t="s">
+        <v>2827</v>
+      </c>
+    </row>
+    <row r="2829" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2829" s="3" t="s">
+        <v>2828</v>
+      </c>
+    </row>
+    <row r="2830" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2830" s="3" t="s">
+        <v>2829</v>
+      </c>
+    </row>
+    <row r="2831" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2831" s="3" t="s">
+        <v>2830</v>
+      </c>
+    </row>
+    <row r="2832" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2832" s="3" t="s">
+        <v>2831</v>
+      </c>
+    </row>
+    <row r="2833" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2833" s="3" t="s">
+        <v>2832</v>
+      </c>
+    </row>
+    <row r="2834" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2834" s="3" t="s">
+        <v>2833</v>
+      </c>
+    </row>
+    <row r="2835" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2835" s="3" t="s">
+        <v>2834</v>
+      </c>
+    </row>
+    <row r="2836" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2836" s="3" t="s">
+        <v>2835</v>
+      </c>
+    </row>
+    <row r="2837" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2837" s="3" t="s">
+        <v>2836</v>
+      </c>
+    </row>
+    <row r="2838" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2838" s="3" t="s">
+        <v>2837</v>
+      </c>
+    </row>
+    <row r="2839" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2839" s="3" t="s">
+        <v>2838</v>
+      </c>
+    </row>
+    <row r="2840" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2840" s="3" t="s">
+        <v>2839</v>
+      </c>
+    </row>
+    <row r="2841" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2841" s="3" t="s">
+        <v>2840</v>
+      </c>
+    </row>
+    <row r="2842" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2842" s="3" t="s">
+        <v>2841</v>
+      </c>
+    </row>
+    <row r="2843" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2843" s="3" t="s">
+        <v>2842</v>
+      </c>
+    </row>
+    <row r="2844" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2844" s="3" t="s">
+        <v>2843</v>
+      </c>
+    </row>
+    <row r="2845" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2845" s="3" t="s">
+        <v>2844</v>
+      </c>
+    </row>
+    <row r="2846" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2846" s="3" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="2847" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2847" s="3" t="s">
+        <v>2846</v>
+      </c>
+    </row>
+    <row r="2848" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2848" s="3" t="s">
+        <v>2847</v>
+      </c>
+    </row>
+    <row r="2849" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2849" s="3" t="s">
+        <v>2848</v>
+      </c>
+    </row>
+    <row r="2850" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2850" s="3" t="s">
+        <v>2849</v>
+      </c>
+    </row>
+    <row r="2851" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2851" s="3" t="s">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="2852" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2852" s="3" t="s">
+        <v>2851</v>
+      </c>
+    </row>
+    <row r="2853" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2853" s="3" t="s">
+        <v>2852</v>
+      </c>
+    </row>
+    <row r="2854" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2854" s="3" t="s">
+        <v>2853</v>
+      </c>
+    </row>
+    <row r="2855" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2855" s="3" t="s">
+        <v>2854</v>
+      </c>
+    </row>
+    <row r="2856" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2856" s="3" t="s">
+        <v>2855</v>
+      </c>
+    </row>
+    <row r="2857" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2857" s="3" t="s">
+        <v>2856</v>
+      </c>
+    </row>
+    <row r="2858" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2858" s="3" t="s">
+        <v>2857</v>
+      </c>
+    </row>
+    <row r="2859" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2859" s="3" t="s">
+        <v>2858</v>
+      </c>
+    </row>
+    <row r="2860" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2860" s="3" t="s">
+        <v>2859</v>
+      </c>
+    </row>
+    <row r="2861" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2861" s="3" t="s">
+        <v>2860</v>
+      </c>
+    </row>
+    <row r="2862" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2862" s="3" t="s">
+        <v>2861</v>
+      </c>
+    </row>
+    <row r="2863" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2863" s="3" t="s">
+        <v>2862</v>
+      </c>
+    </row>
+    <row r="2864" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2864" s="3" t="s">
+        <v>2863</v>
+      </c>
+    </row>
+    <row r="2865" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2865" s="3" t="s">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="2866" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2866" s="3" t="s">
+        <v>2865</v>
+      </c>
+    </row>
+    <row r="2867" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2867" s="3" t="s">
+        <v>2866</v>
+      </c>
+    </row>
+    <row r="2868" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2868" s="3" t="s">
+        <v>2867</v>
+      </c>
+    </row>
+    <row r="2869" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2869" s="3" t="s">
+        <v>2868</v>
+      </c>
+    </row>
+    <row r="2870" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2870" s="3" t="s">
+        <v>2869</v>
+      </c>
+    </row>
+    <row r="2871" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2871" s="3" t="s">
+        <v>2870</v>
+      </c>
+    </row>
+    <row r="2872" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2872" s="3" t="s">
+        <v>2871</v>
+      </c>
+    </row>
+    <row r="2873" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2873" s="3" t="s">
+        <v>2872</v>
+      </c>
+    </row>
+    <row r="2874" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2874" s="3" t="s">
+        <v>2873</v>
+      </c>
+    </row>
+    <row r="2875" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2875" s="3" t="s">
+        <v>2874</v>
+      </c>
+    </row>
+    <row r="2876" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2876" s="3" t="s">
+        <v>2875</v>
+      </c>
+    </row>
+    <row r="2877" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2877" s="3" t="s">
+        <v>2876</v>
+      </c>
+    </row>
+    <row r="2878" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2878" s="3" t="s">
+        <v>2877</v>
+      </c>
+    </row>
+    <row r="2879" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2879" s="3" t="s">
+        <v>2878</v>
+      </c>
+    </row>
+    <row r="2880" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2880" s="3" t="s">
+        <v>2879</v>
+      </c>
+    </row>
+    <row r="2881" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2881" s="3" t="s">
+        <v>2880</v>
+      </c>
+    </row>
+    <row r="2882" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2882" s="3" t="s">
+        <v>2881</v>
+      </c>
+    </row>
+    <row r="2883" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2883" s="3" t="s">
+        <v>2882</v>
+      </c>
+    </row>
+    <row r="2884" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2884" s="3" t="s">
+        <v>2883</v>
+      </c>
+    </row>
+    <row r="2885" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2885" s="3" t="s">
+        <v>2884</v>
+      </c>
+    </row>
+    <row r="2886" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2886" s="3" t="s">
+        <v>2885</v>
+      </c>
+    </row>
+    <row r="2887" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2887" s="3" t="s">
+        <v>2886</v>
+      </c>
+    </row>
+    <row r="2888" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2888" s="3" t="s">
+        <v>2887</v>
+      </c>
+    </row>
+    <row r="2889" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2889" s="3" t="s">
+        <v>2888</v>
+      </c>
+    </row>
+    <row r="2890" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2890" s="3" t="s">
+        <v>2889</v>
+      </c>
+    </row>
+    <row r="2891" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2891" s="3" t="s">
+        <v>2890</v>
+      </c>
+    </row>
+    <row r="2892" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2892" s="3" t="s">
+        <v>2891</v>
+      </c>
+    </row>
+    <row r="2893" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2893" s="3" t="s">
+        <v>2892</v>
+      </c>
+    </row>
+    <row r="2894" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2894" s="3" t="s">
+        <v>2893</v>
+      </c>
+    </row>
+    <row r="2895" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2895" s="3" t="s">
+        <v>2894</v>
+      </c>
+    </row>
+    <row r="2896" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2896" s="3" t="s">
+        <v>2895</v>
+      </c>
+    </row>
+    <row r="2897" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2897" s="3" t="s">
+        <v>2896</v>
+      </c>
+    </row>
+    <row r="2898" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2898" s="3" t="s">
+        <v>2897</v>
+      </c>
+    </row>
+    <row r="2899" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2899" s="3" t="s">
+        <v>2898</v>
+      </c>
+    </row>
+    <row r="2900" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2900" s="3" t="s">
+        <v>2899</v>
+      </c>
+    </row>
+    <row r="2901" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2901" s="3" t="s">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="2902" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2902" s="3" t="s">
+        <v>2901</v>
+      </c>
+    </row>
+    <row r="2903" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2903" s="3" t="s">
+        <v>2902</v>
+      </c>
+    </row>
+    <row r="2904" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2904" s="3" t="s">
+        <v>2903</v>
+      </c>
+    </row>
+    <row r="2905" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2905" s="3" t="s">
+        <v>2904</v>
+      </c>
+    </row>
+    <row r="2906" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2906" s="3" t="s">
+        <v>2905</v>
+      </c>
+    </row>
+    <row r="2907" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2907" s="3" t="s">
+        <v>2906</v>
+      </c>
+    </row>
+    <row r="2908" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2908" s="3" t="s">
+        <v>2907</v>
+      </c>
+    </row>
+    <row r="2909" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2909" s="3" t="s">
+        <v>2908</v>
+      </c>
+    </row>
+    <row r="2910" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2910" s="3" t="s">
+        <v>2909</v>
+      </c>
+    </row>
+    <row r="2911" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2911" s="3" t="s">
+        <v>2910</v>
+      </c>
+    </row>
+    <row r="2912" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2912" s="3" t="s">
+        <v>2911</v>
+      </c>
+    </row>
+    <row r="2913" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2913" s="3" t="s">
+        <v>2912</v>
+      </c>
+    </row>
+    <row r="2914" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2914" s="3" t="s">
+        <v>2913</v>
+      </c>
+    </row>
+    <row r="2915" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2915" s="3" t="s">
+        <v>2914</v>
+      </c>
+    </row>
+    <row r="2916" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2916" s="3" t="s">
+        <v>2915</v>
+      </c>
+    </row>
+    <row r="2917" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2917" s="3" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="2918" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2918" s="3" t="s">
+        <v>2917</v>
+      </c>
+    </row>
+    <row r="2919" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2919" s="3" t="s">
+        <v>2918</v>
+      </c>
+    </row>
+    <row r="2920" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2920" s="3" t="s">
+        <v>2919</v>
+      </c>
+    </row>
+    <row r="2921" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2921" s="3" t="s">
+        <v>2920</v>
+      </c>
+    </row>
+    <row r="2922" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2922" s="3" t="s">
+        <v>2921</v>
+      </c>
+    </row>
+    <row r="2923" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2923" s="3" t="s">
+        <v>2922</v>
+      </c>
+    </row>
+    <row r="2924" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2924" s="3" t="s">
+        <v>2923</v>
+      </c>
+    </row>
+    <row r="2925" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2925" s="3" t="s">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="2926" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2926" s="3" t="s">
+        <v>2925</v>
+      </c>
+    </row>
+    <row r="2927" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2927" s="3" t="s">
+        <v>2926</v>
+      </c>
+    </row>
+    <row r="2928" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2928" s="3" t="s">
+        <v>2927</v>
+      </c>
+    </row>
+    <row r="2929" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2929" s="3" t="s">
+        <v>2928</v>
+      </c>
+    </row>
+    <row r="2930" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2930" s="3" t="s">
+        <v>2929</v>
+      </c>
+    </row>
+    <row r="2931" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2931" s="3" t="s">
+        <v>2930</v>
+      </c>
+    </row>
+    <row r="2932" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2932" s="3" t="s">
+        <v>2931</v>
+      </c>
+    </row>
+    <row r="2933" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2933" s="3" t="s">
+        <v>2932</v>
+      </c>
+    </row>
+    <row r="2934" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2934" s="3" t="s">
+        <v>2933</v>
+      </c>
+    </row>
+    <row r="2935" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2935" s="3" t="s">
+        <v>2934</v>
+      </c>
+    </row>
+    <row r="2936" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2936" s="3" t="s">
+        <v>2935</v>
+      </c>
+    </row>
+    <row r="2937" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2937" s="3" t="s">
+        <v>2936</v>
+      </c>
+    </row>
+    <row r="2938" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2938" s="3" t="s">
+        <v>2937</v>
+      </c>
+    </row>
+    <row r="2939" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2939" s="3" t="s">
+        <v>2938</v>
+      </c>
+    </row>
+    <row r="2940" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2940" s="3" t="s">
+        <v>2939</v>
+      </c>
+    </row>
+    <row r="2941" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2941" s="3" t="s">
+        <v>2940</v>
+      </c>
+    </row>
+    <row r="2942" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2942" s="3" t="s">
+        <v>2941</v>
+      </c>
+    </row>
+    <row r="2943" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2943" s="3" t="s">
+        <v>2942</v>
+      </c>
+    </row>
+    <row r="2944" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2944" s="3" t="s">
+        <v>2943</v>
+      </c>
+    </row>
+    <row r="2945" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2945" s="3" t="s">
+        <v>2944</v>
+      </c>
+    </row>
+    <row r="2946" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2946" s="3" t="s">
+        <v>2945</v>
+      </c>
+    </row>
+    <row r="2947" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2947" s="3" t="s">
+        <v>2946</v>
+      </c>
+    </row>
+    <row r="2948" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2948" s="3" t="s">
+        <v>2947</v>
+      </c>
+    </row>
+    <row r="2949" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2949" s="3" t="s">
+        <v>2948</v>
+      </c>
+    </row>
+    <row r="2950" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2950" s="3" t="s">
+        <v>2949</v>
+      </c>
+    </row>
+    <row r="2951" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2951" s="3" t="s">
+        <v>2950</v>
+      </c>
+    </row>
+    <row r="2952" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2952" s="3" t="s">
+        <v>2951</v>
+      </c>
+    </row>
+    <row r="2953" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2953" s="3" t="s">
+        <v>2952</v>
+      </c>
+    </row>
+    <row r="2954" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2954" s="3" t="s">
+        <v>2953</v>
+      </c>
+    </row>
+    <row r="2955" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2955" s="3" t="s">
+        <v>2954</v>
+      </c>
+    </row>
+    <row r="2956" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2956" s="3" t="s">
+        <v>2955</v>
+      </c>
+    </row>
+    <row r="2957" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2957" s="3" t="s">
+        <v>2956</v>
+      </c>
+    </row>
+    <row r="2958" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2958" s="3" t="s">
+        <v>2957</v>
+      </c>
+    </row>
+    <row r="2959" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2959" s="3" t="s">
+        <v>2958</v>
+      </c>
+    </row>
+    <row r="2960" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2960" s="3" t="s">
+        <v>2959</v>
+      </c>
+    </row>
+    <row r="2961" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2961" s="3" t="s">
+        <v>2960</v>
+      </c>
+    </row>
+    <row r="2962" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2962" s="3" t="s">
+        <v>2961</v>
+      </c>
+    </row>
+    <row r="2963" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2963" s="3" t="s">
+        <v>2962</v>
+      </c>
+    </row>
+    <row r="2964" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2964" s="3" t="s">
+        <v>2963</v>
+      </c>
+    </row>
+    <row r="2965" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2965" s="3" t="s">
+        <v>2964</v>
+      </c>
+    </row>
+    <row r="2966" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2966" s="3" t="s">
+        <v>2965</v>
+      </c>
+    </row>
+    <row r="2967" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2967" s="3" t="s">
+        <v>2966</v>
+      </c>
+    </row>
+    <row r="2968" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2968" s="3" t="s">
+        <v>2967</v>
+      </c>
+    </row>
+    <row r="2969" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2969" s="3" t="s">
+        <v>2968</v>
+      </c>
+    </row>
+    <row r="2970" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2970" s="3" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="2971" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2971" s="3" t="s">
+        <v>2970</v>
+      </c>
+    </row>
+    <row r="2972" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2972" s="3" t="s">
+        <v>2971</v>
+      </c>
+    </row>
+    <row r="2973" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2973" s="3" t="s">
+        <v>2972</v>
+      </c>
+    </row>
+    <row r="2974" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2974" s="3" t="s">
+        <v>2973</v>
+      </c>
+    </row>
+    <row r="2975" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2975" s="3" t="s">
+        <v>2974</v>
+      </c>
+    </row>
+    <row r="2976" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2976" s="3" t="s">
+        <v>2975</v>
+      </c>
+    </row>
+    <row r="2977" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2977" s="3" t="s">
+        <v>2976</v>
+      </c>
+    </row>
+    <row r="2978" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2978" s="3" t="s">
+        <v>2977</v>
+      </c>
+    </row>
+    <row r="2979" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2979" s="3" t="s">
+        <v>2978</v>
+      </c>
+    </row>
+    <row r="2980" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2980" s="3" t="s">
+        <v>2979</v>
+      </c>
+    </row>
+    <row r="2981" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2981" s="3" t="s">
+        <v>2980</v>
+      </c>
+    </row>
+    <row r="2982" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2982" s="3" t="s">
+        <v>2981</v>
+      </c>
+    </row>
+    <row r="2983" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2983" s="3" t="s">
+        <v>2982</v>
+      </c>
+    </row>
+    <row r="2984" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2984" s="3" t="s">
+        <v>2983</v>
+      </c>
+    </row>
+    <row r="2985" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2985" s="3" t="s">
+        <v>2984</v>
+      </c>
+    </row>
+    <row r="2986" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2986" s="3" t="s">
+        <v>2985</v>
+      </c>
+    </row>
+    <row r="2987" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2987" s="3" t="s">
+        <v>2986</v>
+      </c>
+    </row>
+    <row r="2988" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2988" s="3" t="s">
+        <v>2987</v>
+      </c>
+    </row>
+    <row r="2989" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2989" s="3" t="s">
+        <v>2988</v>
+      </c>
+    </row>
+    <row r="2990" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2990" s="3" t="s">
+        <v>2989</v>
+      </c>
+    </row>
+    <row r="2991" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2991" s="3" t="s">
+        <v>2990</v>
+      </c>
+    </row>
+    <row r="2992" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2992" s="3" t="s">
+        <v>2991</v>
+      </c>
+    </row>
+    <row r="2993" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2993" s="3" t="s">
+        <v>2992</v>
+      </c>
+    </row>
+    <row r="2994" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2994" s="3" t="s">
+        <v>2993</v>
+      </c>
+    </row>
+    <row r="2995" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2995" s="3" t="s">
+        <v>2994</v>
+      </c>
+    </row>
+    <row r="2996" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2996" s="3" t="s">
+        <v>2995</v>
+      </c>
+    </row>
+    <row r="2997" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2997" s="3" t="s">
+        <v>2996</v>
+      </c>
+    </row>
+    <row r="2998" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2998" s="3" t="s">
+        <v>2997</v>
+      </c>
+    </row>
+    <row r="2999" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2999" s="3" t="s">
+        <v>2998</v>
+      </c>
+    </row>
+    <row r="3000" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3000" s="3" t="s">
+        <v>2999</v>
+      </c>
+    </row>
+    <row r="3001" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3001" s="3" t="s">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="3002" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3002"/>
+    </row>
+    <row r="3003" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3003"/>
+    </row>
+    <row r="3004" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3004"/>
+    </row>
+    <row r="3005" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3005"/>
+    </row>
+    <row r="3006" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3006"/>
+    </row>
+    <row r="3007" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3007"/>
+    </row>
+    <row r="3008" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3008"/>
+    </row>
+    <row r="3009" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3009"/>
+    </row>
+    <row r="3010" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3010"/>
+    </row>
+    <row r="3011" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3011"/>
+    </row>
+    <row r="3012" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3012"/>
+    </row>
+    <row r="3013" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3013"/>
+    </row>
+    <row r="3014" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3014"/>
+    </row>
+    <row r="3015" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3015"/>
+    </row>
+    <row r="3016" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3016"/>
+    </row>
+    <row r="3017" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3017"/>
+    </row>
+    <row r="3018" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3018"/>
+    </row>
+    <row r="3019" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3019"/>
+    </row>
+    <row r="3020" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3020"/>
+    </row>
+    <row r="3021" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3021"/>
+    </row>
+    <row r="3022" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3022"/>
+    </row>
+    <row r="3023" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3023"/>
+    </row>
+    <row r="3024" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3024"/>
+    </row>
+    <row r="3025" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3025"/>
+    </row>
+    <row r="3026" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3026"/>
+    </row>
+    <row r="3027" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3027"/>
+    </row>
+    <row r="3028" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3028"/>
+    </row>
+    <row r="3029" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3029"/>
+    </row>
+    <row r="3030" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3030"/>
+    </row>
+    <row r="3031" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3031"/>
+    </row>
+    <row r="3032" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3032"/>
+    </row>
+    <row r="3033" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3033"/>
+    </row>
+    <row r="3034" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3034"/>
+    </row>
+    <row r="3035" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3035"/>
+    </row>
+    <row r="3036" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3036"/>
+    </row>
+    <row r="3037" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3037"/>
+    </row>
+    <row r="3038" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3038"/>
+    </row>
+    <row r="3039" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3039"/>
+    </row>
+    <row r="3040" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3040"/>
+    </row>
+    <row r="3041" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3041"/>
+    </row>
+    <row r="3042" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3042"/>
+    </row>
+    <row r="3043" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3043"/>
+    </row>
+    <row r="3044" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3044"/>
+    </row>
+    <row r="3045" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3045"/>
+    </row>
+    <row r="3046" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3046"/>
+    </row>
+    <row r="3047" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3047"/>
+    </row>
+    <row r="3048" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3048"/>
+    </row>
+    <row r="3049" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3049"/>
+    </row>
+    <row r="3050" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3050"/>
+    </row>
+    <row r="3051" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3051"/>
+    </row>
+    <row r="3052" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3052"/>
+    </row>
+    <row r="3053" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3053"/>
+    </row>
+    <row r="3054" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3054"/>
+    </row>
+    <row r="3055" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3055"/>
+    </row>
+    <row r="3056" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3056"/>
+    </row>
+    <row r="3057" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3057"/>
+    </row>
+    <row r="3058" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3058"/>
+    </row>
+    <row r="3059" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3059"/>
+    </row>
+    <row r="3060" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3060"/>
+    </row>
+    <row r="3061" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3061"/>
+    </row>
+    <row r="3062" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3062"/>
+    </row>
+    <row r="3063" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3063"/>
+    </row>
+    <row r="3064" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3064"/>
+    </row>
+    <row r="3065" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3065"/>
+    </row>
+    <row r="3066" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3066"/>
+    </row>
+    <row r="3067" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3067"/>
+    </row>
+    <row r="3068" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3068"/>
+    </row>
+    <row r="3069" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3069"/>
+    </row>
+    <row r="3070" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3070"/>
+    </row>
+    <row r="3071" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3071"/>
+    </row>
+    <row r="3072" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3072"/>
+    </row>
+    <row r="3073" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3073"/>
+    </row>
+    <row r="3074" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3074"/>
+    </row>
+    <row r="3075" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3075"/>
+    </row>
+    <row r="3076" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3076"/>
+    </row>
+    <row r="3077" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3077"/>
+    </row>
+    <row r="3078" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3078"/>
+    </row>
+    <row r="3079" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3079"/>
+    </row>
+    <row r="3080" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3080"/>
+    </row>
+    <row r="3081" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3081"/>
+    </row>
+    <row r="3082" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3082"/>
+    </row>
+    <row r="3083" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3083"/>
+    </row>
+    <row r="3084" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3084"/>
+    </row>
+    <row r="3085" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3085"/>
+    </row>
+    <row r="3086" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3086"/>
+    </row>
+    <row r="3087" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3087"/>
+    </row>
+    <row r="3088" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3088"/>
+    </row>
+    <row r="3089" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3089"/>
+    </row>
+    <row r="3090" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3090"/>
+    </row>
+    <row r="3091" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3091"/>
+    </row>
+    <row r="3092" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3092"/>
+    </row>
+    <row r="3093" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3093"/>
+    </row>
+    <row r="3094" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3094"/>
+    </row>
+    <row r="3095" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3095"/>
+    </row>
+    <row r="3096" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3096"/>
+    </row>
+    <row r="3097" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3097"/>
+    </row>
+    <row r="3098" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3098"/>
+    </row>
+    <row r="3099" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3099"/>
+    </row>
+    <row r="3100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3100"/>
+    </row>
+    <row r="3101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3101"/>
+    </row>
+    <row r="3102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3102"/>
+    </row>
+    <row r="3103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3103"/>
+    </row>
+    <row r="3104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3104"/>
+    </row>
+    <row r="3105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3105"/>
+    </row>
+    <row r="3106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3106"/>
+    </row>
+    <row r="3107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3107"/>
+    </row>
+    <row r="3108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3108"/>
+    </row>
+    <row r="3109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3109"/>
+    </row>
+    <row r="3110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3110"/>
+    </row>
+    <row r="3111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3111"/>
+    </row>
+    <row r="3112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3112"/>
+    </row>
+    <row r="3113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3113"/>
+    </row>
+    <row r="3114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3114"/>
+    </row>
+    <row r="3115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3115"/>
+    </row>
+    <row r="3116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3116"/>
+    </row>
+    <row r="3117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3117"/>
+    </row>
+    <row r="3118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3118"/>
+    </row>
+    <row r="3119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3119"/>
+    </row>
+    <row r="3120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3120"/>
+    </row>
+    <row r="3121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3121"/>
+    </row>
+    <row r="3122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3122"/>
+    </row>
+    <row r="3123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3123"/>
+    </row>
+    <row r="3124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3124"/>
+    </row>
+    <row r="3125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3125"/>
+    </row>
+    <row r="3126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3126"/>
+    </row>
+    <row r="3127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3127"/>
+    </row>
+    <row r="3128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3128"/>
+    </row>
+    <row r="3129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3129"/>
+    </row>
+    <row r="3130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3130"/>
+    </row>
+    <row r="3131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3131"/>
+    </row>
+    <row r="3132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3132"/>
+    </row>
+    <row r="3133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3133"/>
+    </row>
+    <row r="3134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3134"/>
+    </row>
+    <row r="3135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3135"/>
+    </row>
+    <row r="3136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3136"/>
+    </row>
+    <row r="3137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3137"/>
+    </row>
+    <row r="3138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3138"/>
+    </row>
+    <row r="3139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3139"/>
+    </row>
+    <row r="3140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3140"/>
+    </row>
+    <row r="3141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3141"/>
+    </row>
+    <row r="3142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3142"/>
+    </row>
+    <row r="3143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3143"/>
+    </row>
+    <row r="3144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3144"/>
+    </row>
+    <row r="3145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3145"/>
+    </row>
+    <row r="3146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3146"/>
+    </row>
+    <row r="3147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3147"/>
+    </row>
+    <row r="3148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3148"/>
+    </row>
+    <row r="3149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3149"/>
+    </row>
+    <row r="3150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3150"/>
+    </row>
+    <row r="3151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3151"/>
+    </row>
+    <row r="3152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3152"/>
+    </row>
+    <row r="3153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3153"/>
+    </row>
+    <row r="3154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3154"/>
+    </row>
+    <row r="3155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3155"/>
+    </row>
+    <row r="3156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3156"/>
+    </row>
+    <row r="3157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3157"/>
+    </row>
+    <row r="3158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3158"/>
+    </row>
+    <row r="3159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3159"/>
+    </row>
+    <row r="3160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3160"/>
+    </row>
+    <row r="3161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3161"/>
+    </row>
+    <row r="3162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3162"/>
+    </row>
+    <row r="3163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3163"/>
+    </row>
+    <row r="3164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3164"/>
+    </row>
+    <row r="3165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3165"/>
+    </row>
+    <row r="3166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3166"/>
+    </row>
+    <row r="3167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3167"/>
+    </row>
+    <row r="3168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3168"/>
+    </row>
+    <row r="3169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3169"/>
+    </row>
+    <row r="3170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3170"/>
+    </row>
+    <row r="3171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3171"/>
+    </row>
+    <row r="3172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3172"/>
+    </row>
+    <row r="3173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3173"/>
+    </row>
+    <row r="3174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3174"/>
+    </row>
+    <row r="3175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3175"/>
+    </row>
+    <row r="3176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3176"/>
+    </row>
+    <row r="3177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3177"/>
+    </row>
+    <row r="3178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3178"/>
+    </row>
+    <row r="3179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3179"/>
+    </row>
+    <row r="3180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3180"/>
+    </row>
+    <row r="3181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3181"/>
+    </row>
+    <row r="3182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3182"/>
+    </row>
+    <row r="3183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3183"/>
+    </row>
+    <row r="3184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3184"/>
+    </row>
+    <row r="3185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3185"/>
+    </row>
+    <row r="3186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3186"/>
+    </row>
+    <row r="3187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3187"/>
+    </row>
+    <row r="3188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3188"/>
+    </row>
+    <row r="3189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3189"/>
+    </row>
+    <row r="3190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3190"/>
+    </row>
+    <row r="3191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3191"/>
+    </row>
+    <row r="3192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3192"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
